--- a/exams/CSE/19.08.26_Seat_Details_Merged.xlsx
+++ b/exams/CSE/19.08.26_Seat_Details_Merged.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsfgafgjg\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FC61C7-F0A5-4074-A29B-F832A3063C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA9B9B9-E429-4DFC-A8E8-D10E6E6F3A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -1750,6 +1750,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="10"/>
@@ -1893,7 +1896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1936,6 +1939,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1955,43 +1988,34 @@
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2732,7 +2756,7 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="39" customWidth="1"/>
     <col min="3" max="3" width="23.5" customWidth="1"/>
     <col min="4" max="4" width="19.83203125" customWidth="1"/>
     <col min="5" max="5" width="29.83203125" customWidth="1"/>
@@ -2746,19 +2770,19 @@
       <c r="A1" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="32" t="s">
         <v>168</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -2767,7 +2791,7 @@
       <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="17" t="s">
         <v>173</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -2775,25 +2799,25 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32">
+      <c r="B2" s="33">
         <v>46253</v>
       </c>
       <c r="C2" t="s">
         <v>174</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="24" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -2802,68 +2826,68 @@
       <c r="I2" s="8">
         <v>14</v>
       </c>
-      <c r="J2" s="17">
+      <c r="J2" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A3" s="15"/>
-      <c r="B3" s="6"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
       <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I3" s="8">
         <v>14</v>
       </c>
-      <c r="J3" s="18"/>
+      <c r="J3" s="28"/>
     </row>
     <row r="4" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A4" s="15"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="34"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I4" s="8">
         <v>14</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A5" s="15"/>
-      <c r="B5" s="6"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="6"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
       <c r="H5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I5" s="8">
         <v>9</v>
       </c>
-      <c r="J5" s="19"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A6" s="15"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="6"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="14" t="s">
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="24" t="s">
         <v>12</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -2872,84 +2896,84 @@
       <c r="I6" s="8">
         <v>5</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A7" s="15"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I7" s="8">
         <v>14</v>
       </c>
-      <c r="J7" s="18"/>
+      <c r="J7" s="28"/>
     </row>
     <row r="8" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A8" s="15"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="6"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="8">
         <v>14</v>
       </c>
-      <c r="J8" s="18"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A9" s="15"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="6"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I9" s="8">
         <v>14</v>
       </c>
-      <c r="J9" s="18"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A10" s="15"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="6"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="8">
         <v>4</v>
       </c>
-      <c r="J10" s="19"/>
+      <c r="J10" s="29"/>
     </row>
     <row r="11" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A11" s="15"/>
-      <c r="B11" s="6"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="14" t="s">
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="24" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -2958,68 +2982,68 @@
       <c r="I11" s="8">
         <v>10</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A12" s="15"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="6"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I12" s="8">
         <v>14</v>
       </c>
-      <c r="J12" s="18"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A13" s="15"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="34"/>
       <c r="C13" s="6"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="4" t="s">
         <v>19</v>
       </c>
       <c r="I13" s="8">
         <v>14</v>
       </c>
-      <c r="J13" s="18"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A14" s="15"/>
-      <c r="B14" s="6"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="34"/>
       <c r="C14" s="6"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I14" s="8">
         <v>13</v>
       </c>
-      <c r="J14" s="19"/>
+      <c r="J14" s="29"/>
     </row>
     <row r="15" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A15" s="15"/>
-      <c r="B15" s="6"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="34"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="14" t="s">
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="24" t="s">
         <v>22</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -3028,84 +3052,84 @@
       <c r="I15" s="8">
         <v>1</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="27">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A16" s="15"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="34"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
       <c r="H16" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="8">
         <v>14</v>
       </c>
-      <c r="J16" s="18"/>
+      <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A17" s="15"/>
-      <c r="B17" s="6"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="34"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I17" s="8">
         <v>14</v>
       </c>
-      <c r="J17" s="18"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A18" s="15"/>
-      <c r="B18" s="6"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
       <c r="H18" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I18" s="8">
         <v>14</v>
       </c>
-      <c r="J18" s="18"/>
+      <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A19" s="15"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="34"/>
       <c r="C19" s="6"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
       <c r="H19" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I19" s="8">
         <v>7</v>
       </c>
-      <c r="J19" s="19"/>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A20" s="15"/>
-      <c r="B20" s="6"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="6"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="14" t="s">
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="24" t="s">
         <v>27</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -3114,84 +3138,84 @@
       <c r="I20" s="8">
         <v>7</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A21" s="15"/>
-      <c r="B21" s="6"/>
+      <c r="A21" s="25"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="6"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
       <c r="H21" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I21" s="8">
         <v>14</v>
       </c>
-      <c r="J21" s="18"/>
+      <c r="J21" s="28"/>
     </row>
     <row r="22" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A22" s="15"/>
-      <c r="B22" s="6"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="6"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
       <c r="H22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I22" s="8">
         <v>14</v>
       </c>
-      <c r="J22" s="18"/>
+      <c r="J22" s="28"/>
     </row>
     <row r="23" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A23" s="15"/>
-      <c r="B23" s="6"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="6"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
       <c r="H23" s="4" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="8">
         <v>14</v>
       </c>
-      <c r="J23" s="18"/>
+      <c r="J23" s="28"/>
     </row>
     <row r="24" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A24" s="15"/>
-      <c r="B24" s="6"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="34"/>
       <c r="C24" s="6"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
       <c r="H24" s="4" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="8">
         <v>2</v>
       </c>
-      <c r="J24" s="19"/>
+      <c r="J24" s="29"/>
     </row>
     <row r="25" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A25" s="15"/>
-      <c r="B25" s="6"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="34"/>
       <c r="C25" s="6"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="14" t="s">
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="24" t="s">
         <v>33</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -3200,52 +3224,52 @@
       <c r="I25" s="8">
         <v>12</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A26" s="15"/>
-      <c r="B26" s="6"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="6"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
       <c r="H26" s="4" t="s">
         <v>34</v>
       </c>
       <c r="I26" s="8">
         <v>14</v>
       </c>
-      <c r="J26" s="18"/>
+      <c r="J26" s="28"/>
     </row>
     <row r="27" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A27" s="15"/>
-      <c r="B27" s="6"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="34"/>
       <c r="C27" s="6"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
       <c r="H27" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I27" s="8">
         <v>25</v>
       </c>
-      <c r="J27" s="19"/>
+      <c r="J27" s="29"/>
     </row>
     <row r="28" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A28" s="15"/>
-      <c r="B28" s="6"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="6"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="14" t="s">
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="G28" s="24" t="s">
         <v>36</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -3254,36 +3278,36 @@
       <c r="I28" s="8">
         <v>15</v>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A29" s="15"/>
-      <c r="B29" s="6"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
       <c r="H29" s="4" t="s">
         <v>37</v>
       </c>
       <c r="I29" s="8">
         <v>36</v>
       </c>
-      <c r="J29" s="19"/>
+      <c r="J29" s="29"/>
     </row>
     <row r="30" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A30" s="15"/>
-      <c r="B30" s="6"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="6"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="14" t="s">
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="G30" s="24" t="s">
         <v>39</v>
       </c>
       <c r="H30" s="8">
@@ -3292,36 +3316,36 @@
       <c r="I30" s="8">
         <v>27</v>
       </c>
-      <c r="J30" s="17">
+      <c r="J30" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A31" s="15"/>
-      <c r="B31" s="6"/>
+      <c r="A31" s="25"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="6"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
       <c r="H31" s="8">
         <v>213</v>
       </c>
       <c r="I31" s="8">
         <v>24</v>
       </c>
-      <c r="J31" s="19"/>
+      <c r="J31" s="29"/>
     </row>
     <row r="32" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A32" s="15"/>
-      <c r="B32" s="6"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="6"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="14" t="s">
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="24" t="s">
         <v>41</v>
       </c>
       <c r="H32" s="8">
@@ -3330,36 +3354,36 @@
       <c r="I32" s="8">
         <v>24</v>
       </c>
-      <c r="J32" s="17">
+      <c r="J32" s="27">
         <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A33" s="16"/>
-      <c r="B33" s="7"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
       <c r="H33" s="8">
         <v>217</v>
       </c>
       <c r="I33" s="8">
         <v>24</v>
       </c>
-      <c r="J33" s="19"/>
+      <c r="J33" s="29"/>
     </row>
     <row r="34" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A34" s="20"/>
-      <c r="B34" s="9"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="14" t="s">
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="G34" s="14" t="s">
+      <c r="G34" s="24" t="s">
         <v>43</v>
       </c>
       <c r="H34" s="8">
@@ -3368,52 +3392,52 @@
       <c r="I34" s="8">
         <v>24</v>
       </c>
-      <c r="J34" s="17">
+      <c r="J34" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A35" s="21"/>
-      <c r="B35" s="10"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="10"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
       <c r="H35" s="8">
         <v>219</v>
       </c>
       <c r="I35" s="8">
         <v>24</v>
       </c>
-      <c r="J35" s="18"/>
+      <c r="J35" s="28"/>
     </row>
     <row r="36" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A36" s="21"/>
-      <c r="B36" s="10"/>
+      <c r="A36" s="22"/>
+      <c r="B36" s="37"/>
       <c r="C36" s="10"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="8">
         <v>220</v>
       </c>
       <c r="I36" s="8">
         <v>3</v>
       </c>
-      <c r="J36" s="19"/>
+      <c r="J36" s="29"/>
     </row>
     <row r="37" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A37" s="21"/>
-      <c r="B37" s="10"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="10"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="14" t="s">
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="G37" s="14" t="s">
+      <c r="G37" s="24" t="s">
         <v>45</v>
       </c>
       <c r="H37" s="8">
@@ -3422,52 +3446,52 @@
       <c r="I37" s="8">
         <v>21</v>
       </c>
-      <c r="J37" s="17">
+      <c r="J37" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A38" s="21"/>
-      <c r="B38" s="10"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="10"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
       <c r="H38" s="8">
         <v>221</v>
       </c>
       <c r="I38" s="8">
         <v>24</v>
       </c>
-      <c r="J38" s="18"/>
+      <c r="J38" s="28"/>
     </row>
     <row r="39" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A39" s="21"/>
-      <c r="B39" s="10"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="10"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
       <c r="H39" s="8">
         <v>222</v>
       </c>
       <c r="I39" s="8">
         <v>6</v>
       </c>
-      <c r="J39" s="19"/>
+      <c r="J39" s="29"/>
     </row>
     <row r="40" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A40" s="21"/>
-      <c r="B40" s="10"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="10"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="14" t="s">
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="G40" s="14" t="s">
+      <c r="G40" s="24" t="s">
         <v>47</v>
       </c>
       <c r="H40" s="8">
@@ -3476,52 +3500,52 @@
       <c r="I40" s="8">
         <v>18</v>
       </c>
-      <c r="J40" s="17">
+      <c r="J40" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A41" s="21"/>
-      <c r="B41" s="10"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="37"/>
       <c r="C41" s="10"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
       <c r="H41" s="8">
         <v>223</v>
       </c>
       <c r="I41" s="8">
         <v>24</v>
       </c>
-      <c r="J41" s="18"/>
+      <c r="J41" s="28"/>
     </row>
     <row r="42" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A42" s="21"/>
-      <c r="B42" s="10"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
       <c r="H42" s="8">
         <v>224</v>
       </c>
       <c r="I42" s="8">
         <v>9</v>
       </c>
-      <c r="J42" s="19"/>
+      <c r="J42" s="29"/>
     </row>
     <row r="43" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A43" s="21"/>
-      <c r="B43" s="10"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="10"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="14" t="s">
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="G43" s="14" t="s">
+      <c r="G43" s="24" t="s">
         <v>48</v>
       </c>
       <c r="H43" s="8">
@@ -3530,52 +3554,52 @@
       <c r="I43" s="8">
         <v>15</v>
       </c>
-      <c r="J43" s="17">
+      <c r="J43" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A44" s="21"/>
-      <c r="B44" s="10"/>
+      <c r="A44" s="22"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="10"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
       <c r="H44" s="8">
         <v>303</v>
       </c>
       <c r="I44" s="8">
         <v>24</v>
       </c>
-      <c r="J44" s="18"/>
+      <c r="J44" s="28"/>
     </row>
     <row r="45" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A45" s="21"/>
-      <c r="B45" s="10"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="37"/>
       <c r="C45" s="10"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
       <c r="H45" s="8">
         <v>304</v>
       </c>
       <c r="I45" s="8">
         <v>12</v>
       </c>
-      <c r="J45" s="19"/>
+      <c r="J45" s="29"/>
     </row>
     <row r="46" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A46" s="21"/>
-      <c r="B46" s="10"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="10"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="14" t="s">
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="G46" s="14" t="s">
+      <c r="G46" s="24" t="s">
         <v>50</v>
       </c>
       <c r="H46" s="8">
@@ -3584,52 +3608,52 @@
       <c r="I46" s="8">
         <v>12</v>
       </c>
-      <c r="J46" s="17">
+      <c r="J46" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A47" s="21"/>
-      <c r="B47" s="10"/>
+      <c r="A47" s="22"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="10"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
       <c r="H47" s="8">
         <v>305</v>
       </c>
       <c r="I47" s="8">
         <v>24</v>
       </c>
-      <c r="J47" s="18"/>
+      <c r="J47" s="28"/>
     </row>
     <row r="48" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A48" s="21"/>
-      <c r="B48" s="10"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="10"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
       <c r="H48" s="8">
         <v>306</v>
       </c>
       <c r="I48" s="8">
         <v>15</v>
       </c>
-      <c r="J48" s="19"/>
+      <c r="J48" s="29"/>
     </row>
     <row r="49" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A49" s="21"/>
-      <c r="B49" s="10"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="37"/>
       <c r="C49" s="10"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="14" t="s">
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="G49" s="14" t="s">
+      <c r="G49" s="24" t="s">
         <v>52</v>
       </c>
       <c r="H49" s="8">
@@ -3638,52 +3662,52 @@
       <c r="I49" s="8">
         <v>9</v>
       </c>
-      <c r="J49" s="17">
+      <c r="J49" s="27">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A50" s="21"/>
-      <c r="B50" s="10"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="10"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
       <c r="H50" s="8">
         <v>307</v>
       </c>
       <c r="I50" s="8">
         <v>28</v>
       </c>
-      <c r="J50" s="18"/>
+      <c r="J50" s="28"/>
     </row>
     <row r="51" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A51" s="21"/>
-      <c r="B51" s="10"/>
+      <c r="A51" s="22"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="10"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
       <c r="H51" s="4" t="s">
         <v>53</v>
       </c>
       <c r="I51" s="8">
         <v>15</v>
       </c>
-      <c r="J51" s="19"/>
+      <c r="J51" s="29"/>
     </row>
     <row r="52" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A52" s="21"/>
-      <c r="B52" s="10"/>
+      <c r="A52" s="22"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="10"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="14" t="s">
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="G52" s="14" t="s">
+      <c r="G52" s="24" t="s">
         <v>54</v>
       </c>
       <c r="H52" s="4" t="s">
@@ -3692,58 +3716,58 @@
       <c r="I52" s="8">
         <v>9</v>
       </c>
-      <c r="J52" s="17">
+      <c r="J52" s="27">
         <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A53" s="21"/>
-      <c r="B53" s="10"/>
+      <c r="A53" s="22"/>
+      <c r="B53" s="37"/>
       <c r="C53" s="10"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="25"/>
       <c r="H53" s="4" t="s">
         <v>55</v>
       </c>
       <c r="I53" s="8">
         <v>24</v>
       </c>
-      <c r="J53" s="18"/>
+      <c r="J53" s="28"/>
     </row>
     <row r="54" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A54" s="22"/>
-      <c r="B54" s="11"/>
+      <c r="A54" s="23"/>
+      <c r="B54" s="38"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
       <c r="H54" s="8">
         <v>320</v>
       </c>
       <c r="I54" s="8">
         <v>19</v>
       </c>
-      <c r="J54" s="19"/>
+      <c r="J54" s="29"/>
     </row>
     <row r="55" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B55" s="5"/>
+      <c r="B55" s="33"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="G55" s="14" t="s">
+      <c r="G55" s="24" t="s">
         <v>59</v>
       </c>
       <c r="H55" s="4" t="s">
@@ -3752,84 +3776,84 @@
       <c r="I55" s="8">
         <v>11</v>
       </c>
-      <c r="J55" s="17">
+      <c r="J55" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A56" s="15"/>
-      <c r="B56" s="6"/>
+      <c r="A56" s="25"/>
+      <c r="B56" s="34"/>
       <c r="C56" s="6"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
       <c r="H56" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I56" s="8">
         <v>11</v>
       </c>
-      <c r="J56" s="18"/>
+      <c r="J56" s="28"/>
     </row>
     <row r="57" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A57" s="15"/>
-      <c r="B57" s="6"/>
+      <c r="A57" s="25"/>
+      <c r="B57" s="34"/>
       <c r="C57" s="6"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
       <c r="H57" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I57" s="8">
         <v>11</v>
       </c>
-      <c r="J57" s="18"/>
+      <c r="J57" s="28"/>
     </row>
     <row r="58" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A58" s="15"/>
-      <c r="B58" s="6"/>
+      <c r="A58" s="25"/>
+      <c r="B58" s="34"/>
       <c r="C58" s="6"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
       <c r="H58" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I58" s="8">
         <v>11</v>
       </c>
-      <c r="J58" s="18"/>
+      <c r="J58" s="28"/>
     </row>
     <row r="59" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A59" s="15"/>
-      <c r="B59" s="6"/>
+      <c r="A59" s="25"/>
+      <c r="B59" s="34"/>
       <c r="C59" s="6"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
       <c r="H59" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I59" s="8">
         <v>7</v>
       </c>
-      <c r="J59" s="19"/>
+      <c r="J59" s="29"/>
     </row>
     <row r="60" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A60" s="15"/>
-      <c r="B60" s="6"/>
+      <c r="A60" s="25"/>
+      <c r="B60" s="34"/>
       <c r="C60" s="6"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="14" t="s">
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="G60" s="14" t="s">
+      <c r="G60" s="24" t="s">
         <v>61</v>
       </c>
       <c r="H60" s="4" t="s">
@@ -3838,84 +3862,84 @@
       <c r="I60" s="8">
         <v>4</v>
       </c>
-      <c r="J60" s="17">
+      <c r="J60" s="27">
         <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A61" s="15"/>
-      <c r="B61" s="6"/>
+      <c r="A61" s="25"/>
+      <c r="B61" s="34"/>
       <c r="C61" s="6"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
       <c r="H61" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I61" s="8">
         <v>11</v>
       </c>
-      <c r="J61" s="18"/>
+      <c r="J61" s="28"/>
     </row>
     <row r="62" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A62" s="15"/>
-      <c r="B62" s="6"/>
+      <c r="A62" s="25"/>
+      <c r="B62" s="34"/>
       <c r="C62" s="6"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
       <c r="H62" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="8">
         <v>11</v>
       </c>
-      <c r="J62" s="18"/>
+      <c r="J62" s="28"/>
     </row>
     <row r="63" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A63" s="15"/>
-      <c r="B63" s="6"/>
+      <c r="A63" s="25"/>
+      <c r="B63" s="34"/>
       <c r="C63" s="6"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
       <c r="H63" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I63" s="8">
         <v>11</v>
       </c>
-      <c r="J63" s="18"/>
+      <c r="J63" s="28"/>
     </row>
     <row r="64" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A64" s="15"/>
-      <c r="B64" s="6"/>
+      <c r="A64" s="25"/>
+      <c r="B64" s="34"/>
       <c r="C64" s="6"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
       <c r="H64" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I64" s="8">
         <v>2</v>
       </c>
-      <c r="J64" s="19"/>
+      <c r="J64" s="29"/>
     </row>
     <row r="65" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A65" s="15"/>
-      <c r="B65" s="6"/>
+      <c r="A65" s="25"/>
+      <c r="B65" s="34"/>
       <c r="C65" s="6"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="14" t="s">
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="G65" s="14" t="s">
+      <c r="G65" s="24" t="s">
         <v>62</v>
       </c>
       <c r="H65" s="4" t="s">
@@ -3924,84 +3948,84 @@
       <c r="I65" s="8">
         <v>9</v>
       </c>
-      <c r="J65" s="17">
+      <c r="J65" s="27">
         <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A66" s="16"/>
-      <c r="B66" s="7"/>
+      <c r="A66" s="26"/>
+      <c r="B66" s="35"/>
       <c r="C66" s="7"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
       <c r="H66" s="4" t="s">
         <v>19</v>
       </c>
       <c r="I66" s="8">
         <v>11</v>
       </c>
-      <c r="J66" s="19"/>
+      <c r="J66" s="29"/>
     </row>
     <row r="67" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A67" s="20"/>
-      <c r="B67" s="9"/>
+      <c r="A67" s="21"/>
+      <c r="B67" s="36"/>
       <c r="C67" s="9"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
       <c r="H67" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I67" s="8">
         <v>11</v>
       </c>
-      <c r="J67" s="20"/>
+      <c r="J67" s="21"/>
     </row>
     <row r="68" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A68" s="21"/>
-      <c r="B68" s="10"/>
+      <c r="A68" s="22"/>
+      <c r="B68" s="37"/>
       <c r="C68" s="10"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
       <c r="H68" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I68" s="8">
         <v>11</v>
       </c>
-      <c r="J68" s="21"/>
+      <c r="J68" s="22"/>
     </row>
     <row r="69" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A69" s="21"/>
-      <c r="B69" s="10"/>
+      <c r="A69" s="22"/>
+      <c r="B69" s="37"/>
       <c r="C69" s="10"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
       <c r="H69" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I69" s="8">
         <v>6</v>
       </c>
-      <c r="J69" s="22"/>
+      <c r="J69" s="23"/>
     </row>
     <row r="70" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A70" s="21"/>
-      <c r="B70" s="10"/>
+      <c r="A70" s="22"/>
+      <c r="B70" s="37"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="14" t="s">
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G70" s="14" t="s">
+      <c r="G70" s="24" t="s">
         <v>64</v>
       </c>
       <c r="H70" s="4" t="s">
@@ -4010,100 +4034,100 @@
       <c r="I70" s="8">
         <v>5</v>
       </c>
-      <c r="J70" s="17">
+      <c r="J70" s="27">
         <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A71" s="21"/>
-      <c r="B71" s="10"/>
+      <c r="A71" s="22"/>
+      <c r="B71" s="37"/>
       <c r="C71" s="10"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
       <c r="H71" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I71" s="8">
         <v>11</v>
       </c>
-      <c r="J71" s="18"/>
+      <c r="J71" s="28"/>
     </row>
     <row r="72" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A72" s="21"/>
-      <c r="B72" s="10"/>
+      <c r="A72" s="22"/>
+      <c r="B72" s="37"/>
       <c r="C72" s="10"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="15"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
       <c r="H72" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I72" s="8">
         <v>11</v>
       </c>
-      <c r="J72" s="18"/>
+      <c r="J72" s="28"/>
     </row>
     <row r="73" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A73" s="21"/>
-      <c r="B73" s="10"/>
+      <c r="A73" s="22"/>
+      <c r="B73" s="37"/>
       <c r="C73" s="10"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="15"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
       <c r="H73" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I73" s="8">
         <v>11</v>
       </c>
-      <c r="J73" s="18"/>
+      <c r="J73" s="28"/>
     </row>
     <row r="74" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A74" s="21"/>
-      <c r="B74" s="10"/>
+      <c r="A74" s="22"/>
+      <c r="B74" s="37"/>
       <c r="C74" s="10"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="15"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
       <c r="H74" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I74" s="8">
         <v>11</v>
       </c>
-      <c r="J74" s="18"/>
+      <c r="J74" s="28"/>
     </row>
     <row r="75" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A75" s="21"/>
-      <c r="B75" s="10"/>
+      <c r="A75" s="22"/>
+      <c r="B75" s="37"/>
       <c r="C75" s="10"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
       <c r="H75" s="4" t="s">
         <v>30</v>
       </c>
       <c r="I75" s="8">
         <v>1</v>
       </c>
-      <c r="J75" s="19"/>
+      <c r="J75" s="29"/>
     </row>
     <row r="76" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A76" s="21"/>
-      <c r="B76" s="10"/>
+      <c r="A76" s="22"/>
+      <c r="B76" s="37"/>
       <c r="C76" s="10"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="14" t="s">
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="G76" s="14" t="s">
+      <c r="G76" s="24" t="s">
         <v>66</v>
       </c>
       <c r="H76" s="4" t="s">
@@ -4112,68 +4136,68 @@
       <c r="I76" s="8">
         <v>10</v>
       </c>
-      <c r="J76" s="17">
+      <c r="J76" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A77" s="21"/>
-      <c r="B77" s="10"/>
+      <c r="A77" s="22"/>
+      <c r="B77" s="37"/>
       <c r="C77" s="10"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
       <c r="H77" s="4" t="s">
         <v>31</v>
       </c>
       <c r="I77" s="8">
         <v>11</v>
       </c>
-      <c r="J77" s="18"/>
+      <c r="J77" s="28"/>
     </row>
     <row r="78" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A78" s="21"/>
-      <c r="B78" s="10"/>
+      <c r="A78" s="22"/>
+      <c r="B78" s="37"/>
       <c r="C78" s="10"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="15"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
       <c r="H78" s="4" t="s">
         <v>34</v>
       </c>
       <c r="I78" s="8">
         <v>11</v>
       </c>
-      <c r="J78" s="18"/>
+      <c r="J78" s="28"/>
     </row>
     <row r="79" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A79" s="21"/>
-      <c r="B79" s="10"/>
+      <c r="A79" s="22"/>
+      <c r="B79" s="37"/>
       <c r="C79" s="10"/>
-      <c r="D79" s="21"/>
-      <c r="E79" s="21"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
       <c r="H79" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I79" s="8">
         <v>19</v>
       </c>
-      <c r="J79" s="19"/>
+      <c r="J79" s="29"/>
     </row>
     <row r="80" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A80" s="21"/>
-      <c r="B80" s="10"/>
+      <c r="A80" s="22"/>
+      <c r="B80" s="37"/>
       <c r="C80" s="10"/>
-      <c r="D80" s="21"/>
-      <c r="E80" s="21"/>
-      <c r="F80" s="14" t="s">
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="G80" s="14" t="s">
+      <c r="G80" s="24" t="s">
         <v>67</v>
       </c>
       <c r="H80" s="4" t="s">
@@ -4182,52 +4206,52 @@
       <c r="I80" s="8">
         <v>13</v>
       </c>
-      <c r="J80" s="17">
+      <c r="J80" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A81" s="21"/>
-      <c r="B81" s="10"/>
+      <c r="A81" s="22"/>
+      <c r="B81" s="37"/>
       <c r="C81" s="10"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="15"/>
-      <c r="G81" s="15"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="25"/>
+      <c r="G81" s="25"/>
       <c r="H81" s="4" t="s">
         <v>37</v>
       </c>
       <c r="I81" s="8">
         <v>36</v>
       </c>
-      <c r="J81" s="18"/>
+      <c r="J81" s="28"/>
     </row>
     <row r="82" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A82" s="21"/>
-      <c r="B82" s="10"/>
+      <c r="A82" s="22"/>
+      <c r="B82" s="37"/>
       <c r="C82" s="10"/>
-      <c r="D82" s="21"/>
-      <c r="E82" s="21"/>
-      <c r="F82" s="16"/>
-      <c r="G82" s="16"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="26"/>
       <c r="H82" s="8">
         <v>208</v>
       </c>
       <c r="I82" s="8">
         <v>2</v>
       </c>
-      <c r="J82" s="19"/>
+      <c r="J82" s="29"/>
     </row>
     <row r="83" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A83" s="21"/>
-      <c r="B83" s="10"/>
+      <c r="A83" s="22"/>
+      <c r="B83" s="37"/>
       <c r="C83" s="10"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="14" t="s">
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="G83" s="14" t="s">
+      <c r="G83" s="24" t="s">
         <v>69</v>
       </c>
       <c r="H83" s="8">
@@ -4236,52 +4260,52 @@
       <c r="I83" s="8">
         <v>16</v>
       </c>
-      <c r="J83" s="17">
+      <c r="J83" s="27">
         <v>48</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A84" s="21"/>
-      <c r="B84" s="10"/>
+      <c r="A84" s="22"/>
+      <c r="B84" s="37"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="21"/>
-      <c r="E84" s="21"/>
-      <c r="F84" s="15"/>
-      <c r="G84" s="15"/>
+      <c r="D84" s="22"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
       <c r="H84" s="8">
         <v>213</v>
       </c>
       <c r="I84" s="8">
         <v>24</v>
       </c>
-      <c r="J84" s="18"/>
+      <c r="J84" s="28"/>
     </row>
     <row r="85" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A85" s="21"/>
-      <c r="B85" s="10"/>
+      <c r="A85" s="22"/>
+      <c r="B85" s="37"/>
       <c r="C85" s="10"/>
-      <c r="D85" s="21"/>
-      <c r="E85" s="21"/>
-      <c r="F85" s="16"/>
-      <c r="G85" s="16"/>
+      <c r="D85" s="22"/>
+      <c r="E85" s="22"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
       <c r="H85" s="8">
         <v>216</v>
       </c>
       <c r="I85" s="8">
         <v>8</v>
       </c>
-      <c r="J85" s="19"/>
+      <c r="J85" s="29"/>
     </row>
     <row r="86" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A86" s="21"/>
-      <c r="B86" s="10"/>
+      <c r="A86" s="22"/>
+      <c r="B86" s="37"/>
       <c r="C86" s="10"/>
-      <c r="D86" s="21"/>
-      <c r="E86" s="21"/>
-      <c r="F86" s="14" t="s">
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="F86" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="G86" s="14" t="s">
+      <c r="G86" s="24" t="s">
         <v>70</v>
       </c>
       <c r="H86" s="8">
@@ -4290,52 +4314,52 @@
       <c r="I86" s="8">
         <v>16</v>
       </c>
-      <c r="J86" s="17">
+      <c r="J86" s="27">
         <v>48</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A87" s="21"/>
-      <c r="B87" s="10"/>
+      <c r="A87" s="22"/>
+      <c r="B87" s="37"/>
       <c r="C87" s="10"/>
-      <c r="D87" s="21"/>
-      <c r="E87" s="21"/>
-      <c r="F87" s="15"/>
-      <c r="G87" s="15"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="F87" s="25"/>
+      <c r="G87" s="25"/>
       <c r="H87" s="8">
         <v>217</v>
       </c>
       <c r="I87" s="8">
         <v>24</v>
       </c>
-      <c r="J87" s="18"/>
+      <c r="J87" s="28"/>
     </row>
     <row r="88" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A88" s="21"/>
-      <c r="B88" s="10"/>
+      <c r="A88" s="22"/>
+      <c r="B88" s="37"/>
       <c r="C88" s="10"/>
-      <c r="D88" s="21"/>
-      <c r="E88" s="21"/>
-      <c r="F88" s="16"/>
-      <c r="G88" s="16"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="26"/>
+      <c r="G88" s="26"/>
       <c r="H88" s="8">
         <v>218</v>
       </c>
       <c r="I88" s="8">
         <v>8</v>
       </c>
-      <c r="J88" s="19"/>
+      <c r="J88" s="29"/>
     </row>
     <row r="89" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A89" s="21"/>
-      <c r="B89" s="10"/>
+      <c r="A89" s="22"/>
+      <c r="B89" s="37"/>
       <c r="C89" s="10"/>
-      <c r="D89" s="21"/>
-      <c r="E89" s="21"/>
-      <c r="F89" s="14" t="s">
+      <c r="D89" s="22"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="G89" s="14" t="s">
+      <c r="G89" s="24" t="s">
         <v>71</v>
       </c>
       <c r="H89" s="8">
@@ -4344,52 +4368,52 @@
       <c r="I89" s="8">
         <v>16</v>
       </c>
-      <c r="J89" s="17">
+      <c r="J89" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A90" s="21"/>
-      <c r="B90" s="10"/>
+      <c r="A90" s="22"/>
+      <c r="B90" s="37"/>
       <c r="C90" s="10"/>
-      <c r="D90" s="21"/>
-      <c r="E90" s="21"/>
-      <c r="F90" s="15"/>
-      <c r="G90" s="15"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="25"/>
       <c r="H90" s="8">
         <v>219</v>
       </c>
       <c r="I90" s="8">
         <v>24</v>
       </c>
-      <c r="J90" s="18"/>
+      <c r="J90" s="28"/>
     </row>
     <row r="91" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A91" s="21"/>
-      <c r="B91" s="10"/>
+      <c r="A91" s="22"/>
+      <c r="B91" s="37"/>
       <c r="C91" s="10"/>
-      <c r="D91" s="21"/>
-      <c r="E91" s="21"/>
-      <c r="F91" s="16"/>
-      <c r="G91" s="16"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="26"/>
+      <c r="G91" s="26"/>
       <c r="H91" s="8">
         <v>220</v>
       </c>
       <c r="I91" s="8">
         <v>11</v>
       </c>
-      <c r="J91" s="19"/>
+      <c r="J91" s="29"/>
     </row>
     <row r="92" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A92" s="21"/>
-      <c r="B92" s="10"/>
+      <c r="A92" s="22"/>
+      <c r="B92" s="37"/>
       <c r="C92" s="10"/>
-      <c r="D92" s="21"/>
-      <c r="E92" s="21"/>
-      <c r="F92" s="14" t="s">
+      <c r="D92" s="22"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G92" s="14" t="s">
+      <c r="G92" s="24" t="s">
         <v>72</v>
       </c>
       <c r="H92" s="8">
@@ -4398,52 +4422,52 @@
       <c r="I92" s="8">
         <v>13</v>
       </c>
-      <c r="J92" s="17">
+      <c r="J92" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A93" s="21"/>
-      <c r="B93" s="10"/>
+      <c r="A93" s="22"/>
+      <c r="B93" s="37"/>
       <c r="C93" s="10"/>
-      <c r="D93" s="21"/>
-      <c r="E93" s="21"/>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15"/>
+      <c r="D93" s="22"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="25"/>
+      <c r="G93" s="25"/>
       <c r="H93" s="8">
         <v>221</v>
       </c>
       <c r="I93" s="8">
         <v>24</v>
       </c>
-      <c r="J93" s="18"/>
+      <c r="J93" s="28"/>
     </row>
     <row r="94" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A94" s="21"/>
-      <c r="B94" s="10"/>
+      <c r="A94" s="22"/>
+      <c r="B94" s="37"/>
       <c r="C94" s="10"/>
-      <c r="D94" s="21"/>
-      <c r="E94" s="21"/>
-      <c r="F94" s="16"/>
-      <c r="G94" s="16"/>
+      <c r="D94" s="22"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="26"/>
+      <c r="G94" s="26"/>
       <c r="H94" s="8">
         <v>222</v>
       </c>
       <c r="I94" s="8">
         <v>14</v>
       </c>
-      <c r="J94" s="19"/>
+      <c r="J94" s="29"/>
     </row>
     <row r="95" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A95" s="21"/>
-      <c r="B95" s="10"/>
+      <c r="A95" s="22"/>
+      <c r="B95" s="37"/>
       <c r="C95" s="10"/>
-      <c r="D95" s="21"/>
-      <c r="E95" s="21"/>
-      <c r="F95" s="14" t="s">
+      <c r="D95" s="22"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="G95" s="14" t="s">
+      <c r="G95" s="24" t="s">
         <v>74</v>
       </c>
       <c r="H95" s="8">
@@ -4452,52 +4476,52 @@
       <c r="I95" s="8">
         <v>10</v>
       </c>
-      <c r="J95" s="17">
+      <c r="J95" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A96" s="21"/>
-      <c r="B96" s="10"/>
+      <c r="A96" s="22"/>
+      <c r="B96" s="37"/>
       <c r="C96" s="10"/>
-      <c r="D96" s="21"/>
-      <c r="E96" s="21"/>
-      <c r="F96" s="15"/>
-      <c r="G96" s="15"/>
+      <c r="D96" s="22"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
       <c r="H96" s="8">
         <v>223</v>
       </c>
       <c r="I96" s="8">
         <v>24</v>
       </c>
-      <c r="J96" s="18"/>
+      <c r="J96" s="28"/>
     </row>
     <row r="97" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A97" s="21"/>
-      <c r="B97" s="10"/>
+      <c r="A97" s="22"/>
+      <c r="B97" s="37"/>
       <c r="C97" s="10"/>
-      <c r="D97" s="21"/>
-      <c r="E97" s="21"/>
-      <c r="F97" s="16"/>
-      <c r="G97" s="16"/>
+      <c r="D97" s="22"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="26"/>
+      <c r="G97" s="26"/>
       <c r="H97" s="8">
         <v>224</v>
       </c>
       <c r="I97" s="8">
         <v>17</v>
       </c>
-      <c r="J97" s="19"/>
+      <c r="J97" s="29"/>
     </row>
     <row r="98" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A98" s="21"/>
-      <c r="B98" s="10"/>
+      <c r="A98" s="22"/>
+      <c r="B98" s="37"/>
       <c r="C98" s="10"/>
-      <c r="D98" s="21"/>
-      <c r="E98" s="21"/>
-      <c r="F98" s="14" t="s">
+      <c r="D98" s="22"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="G98" s="14" t="s">
+      <c r="G98" s="24" t="s">
         <v>75</v>
       </c>
       <c r="H98" s="8">
@@ -4506,32 +4530,32 @@
       <c r="I98" s="8">
         <v>7</v>
       </c>
-      <c r="J98" s="17">
+      <c r="J98" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="21" customHeight="1">
-      <c r="A99" s="22"/>
-      <c r="B99" s="11"/>
+      <c r="A99" s="23"/>
+      <c r="B99" s="38"/>
       <c r="C99" s="11"/>
-      <c r="D99" s="22"/>
-      <c r="E99" s="22"/>
-      <c r="F99" s="16"/>
-      <c r="G99" s="16"/>
+      <c r="D99" s="23"/>
+      <c r="E99" s="23"/>
+      <c r="F99" s="26"/>
+      <c r="G99" s="26"/>
       <c r="H99" s="8">
         <v>303</v>
       </c>
       <c r="I99" s="8">
         <v>24</v>
       </c>
-      <c r="J99" s="19"/>
+      <c r="J99" s="29"/>
     </row>
     <row r="100" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A100" s="20"/>
-      <c r="B100" s="9"/>
+      <c r="A100" s="21"/>
+      <c r="B100" s="36"/>
       <c r="C100" s="9"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="21"/>
       <c r="F100" s="13"/>
       <c r="G100" s="13"/>
       <c r="H100" s="8">
@@ -4543,15 +4567,15 @@
       <c r="J100" s="13"/>
     </row>
     <row r="101" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A101" s="21"/>
-      <c r="B101" s="10"/>
+      <c r="A101" s="22"/>
+      <c r="B101" s="37"/>
       <c r="C101" s="10"/>
-      <c r="D101" s="21"/>
-      <c r="E101" s="21"/>
-      <c r="F101" s="14" t="s">
+      <c r="D101" s="22"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="G101" s="14" t="s">
+      <c r="G101" s="24" t="s">
         <v>77</v>
       </c>
       <c r="H101" s="8">
@@ -4560,52 +4584,52 @@
       <c r="I101" s="8">
         <v>4</v>
       </c>
-      <c r="J101" s="17">
+      <c r="J101" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A102" s="21"/>
-      <c r="B102" s="10"/>
+      <c r="A102" s="22"/>
+      <c r="B102" s="37"/>
       <c r="C102" s="10"/>
-      <c r="D102" s="21"/>
-      <c r="E102" s="21"/>
-      <c r="F102" s="15"/>
-      <c r="G102" s="15"/>
+      <c r="D102" s="22"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="25"/>
+      <c r="G102" s="25"/>
       <c r="H102" s="8">
         <v>305</v>
       </c>
       <c r="I102" s="8">
         <v>24</v>
       </c>
-      <c r="J102" s="18"/>
+      <c r="J102" s="28"/>
     </row>
     <row r="103" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A103" s="21"/>
-      <c r="B103" s="10"/>
+      <c r="A103" s="22"/>
+      <c r="B103" s="37"/>
       <c r="C103" s="10"/>
-      <c r="D103" s="21"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="16"/>
-      <c r="G103" s="16"/>
+      <c r="D103" s="22"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="26"/>
+      <c r="G103" s="26"/>
       <c r="H103" s="8">
         <v>306</v>
       </c>
       <c r="I103" s="8">
         <v>23</v>
       </c>
-      <c r="J103" s="19"/>
+      <c r="J103" s="29"/>
     </row>
     <row r="104" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A104" s="21"/>
-      <c r="B104" s="10"/>
+      <c r="A104" s="22"/>
+      <c r="B104" s="37"/>
       <c r="C104" s="10"/>
-      <c r="D104" s="21"/>
-      <c r="E104" s="21"/>
-      <c r="F104" s="14" t="s">
+      <c r="D104" s="22"/>
+      <c r="E104" s="22"/>
+      <c r="F104" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="G104" s="14" t="s">
+      <c r="G104" s="24" t="s">
         <v>78</v>
       </c>
       <c r="H104" s="8">
@@ -4614,68 +4638,68 @@
       <c r="I104" s="8">
         <v>1</v>
       </c>
-      <c r="J104" s="17">
+      <c r="J104" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A105" s="21"/>
-      <c r="B105" s="10"/>
+      <c r="A105" s="22"/>
+      <c r="B105" s="37"/>
       <c r="C105" s="10"/>
-      <c r="D105" s="21"/>
-      <c r="E105" s="21"/>
-      <c r="F105" s="15"/>
-      <c r="G105" s="15"/>
+      <c r="D105" s="22"/>
+      <c r="E105" s="22"/>
+      <c r="F105" s="25"/>
+      <c r="G105" s="25"/>
       <c r="H105" s="8">
         <v>307</v>
       </c>
       <c r="I105" s="8">
         <v>20</v>
       </c>
-      <c r="J105" s="18"/>
+      <c r="J105" s="28"/>
     </row>
     <row r="106" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A106" s="21"/>
-      <c r="B106" s="10"/>
+      <c r="A106" s="22"/>
+      <c r="B106" s="37"/>
       <c r="C106" s="10"/>
-      <c r="D106" s="21"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="15"/>
-      <c r="G106" s="15"/>
+      <c r="D106" s="22"/>
+      <c r="E106" s="22"/>
+      <c r="F106" s="25"/>
+      <c r="G106" s="25"/>
       <c r="H106" s="4" t="s">
         <v>53</v>
       </c>
       <c r="I106" s="8">
         <v>24</v>
       </c>
-      <c r="J106" s="18"/>
+      <c r="J106" s="28"/>
     </row>
     <row r="107" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A107" s="21"/>
-      <c r="B107" s="10"/>
+      <c r="A107" s="22"/>
+      <c r="B107" s="37"/>
       <c r="C107" s="10"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="21"/>
-      <c r="F107" s="16"/>
-      <c r="G107" s="16"/>
+      <c r="D107" s="22"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="26"/>
+      <c r="G107" s="26"/>
       <c r="H107" s="4" t="s">
         <v>55</v>
       </c>
       <c r="I107" s="8">
         <v>6</v>
       </c>
-      <c r="J107" s="19"/>
+      <c r="J107" s="29"/>
     </row>
     <row r="108" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A108" s="21"/>
-      <c r="B108" s="10"/>
+      <c r="A108" s="22"/>
+      <c r="B108" s="37"/>
       <c r="C108" s="10"/>
-      <c r="D108" s="21"/>
-      <c r="E108" s="21"/>
-      <c r="F108" s="14" t="s">
+      <c r="D108" s="22"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="G108" s="14" t="s">
+      <c r="G108" s="24" t="s">
         <v>80</v>
       </c>
       <c r="H108" s="4" t="s">
@@ -4684,78 +4708,122 @@
       <c r="I108" s="8">
         <v>18</v>
       </c>
-      <c r="J108" s="17">
+      <c r="J108" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A109" s="21"/>
-      <c r="B109" s="10"/>
+      <c r="A109" s="22"/>
+      <c r="B109" s="37"/>
       <c r="C109" s="10"/>
-      <c r="D109" s="21"/>
-      <c r="E109" s="21"/>
-      <c r="F109" s="15"/>
-      <c r="G109" s="15"/>
+      <c r="D109" s="22"/>
+      <c r="E109" s="22"/>
+      <c r="F109" s="25"/>
+      <c r="G109" s="25"/>
       <c r="H109" s="8">
         <v>320</v>
       </c>
       <c r="I109" s="8">
         <v>33</v>
       </c>
-      <c r="J109" s="18"/>
+      <c r="J109" s="28"/>
     </row>
     <row r="110" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A110" s="22"/>
-      <c r="B110" s="11"/>
+      <c r="A110" s="23"/>
+      <c r="B110" s="38"/>
       <c r="C110" s="11"/>
-      <c r="D110" s="22"/>
-      <c r="E110" s="22"/>
-      <c r="F110" s="16"/>
-      <c r="G110" s="16"/>
+      <c r="D110" s="23"/>
+      <c r="E110" s="23"/>
+      <c r="F110" s="26"/>
+      <c r="G110" s="26"/>
       <c r="H110" s="13"/>
       <c r="I110" s="13"/>
-      <c r="J110" s="19"/>
+      <c r="J110" s="29"/>
     </row>
     <row r="111" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A111" s="23" t="s">
+      <c r="A111" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B111" s="24"/>
-      <c r="C111" s="24"/>
-      <c r="D111" s="24"/>
-      <c r="E111" s="24"/>
-      <c r="F111" s="24"/>
-      <c r="G111" s="24"/>
-      <c r="H111" s="24"/>
-      <c r="I111" s="25"/>
+      <c r="B111" s="19"/>
+      <c r="C111" s="19"/>
+      <c r="D111" s="19"/>
+      <c r="E111" s="19"/>
+      <c r="F111" s="19"/>
+      <c r="G111" s="19"/>
+      <c r="H111" s="19"/>
+      <c r="I111" s="20"/>
       <c r="J111" s="8">
         <v>1557</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="A111:I111"/>
-    <mergeCell ref="A100:A110"/>
-    <mergeCell ref="D100:D110"/>
-    <mergeCell ref="E100:E110"/>
-    <mergeCell ref="F101:F103"/>
-    <mergeCell ref="G101:G103"/>
-    <mergeCell ref="J101:J103"/>
-    <mergeCell ref="F104:F107"/>
-    <mergeCell ref="G104:G107"/>
-    <mergeCell ref="J104:J107"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="J108:J110"/>
-    <mergeCell ref="F92:F94"/>
-    <mergeCell ref="G92:G94"/>
-    <mergeCell ref="J92:J94"/>
-    <mergeCell ref="F95:F97"/>
-    <mergeCell ref="G95:G97"/>
-    <mergeCell ref="J95:J97"/>
-    <mergeCell ref="F98:F99"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="J98:J99"/>
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="D2:D33"/>
+    <mergeCell ref="E2:E33"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="G2:G5"/>
+    <mergeCell ref="J2:J5"/>
+    <mergeCell ref="F6:F10"/>
+    <mergeCell ref="G6:G10"/>
+    <mergeCell ref="J6:J10"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="G11:G14"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="F15:F19"/>
+    <mergeCell ref="G15:G19"/>
+    <mergeCell ref="J15:J19"/>
+    <mergeCell ref="F20:F24"/>
+    <mergeCell ref="G20:G24"/>
+    <mergeCell ref="J20:J24"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="A34:A54"/>
+    <mergeCell ref="D34:D54"/>
+    <mergeCell ref="E34:E54"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="J34:J36"/>
+    <mergeCell ref="F37:F39"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="J37:J39"/>
+    <mergeCell ref="F40:F42"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="J40:J42"/>
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="J43:J45"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="J46:J48"/>
+    <mergeCell ref="F49:F51"/>
+    <mergeCell ref="G49:G51"/>
+    <mergeCell ref="J49:J51"/>
+    <mergeCell ref="F52:F54"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="J52:J54"/>
+    <mergeCell ref="A55:A66"/>
+    <mergeCell ref="D55:D66"/>
+    <mergeCell ref="E55:E66"/>
+    <mergeCell ref="F55:F59"/>
+    <mergeCell ref="G55:G59"/>
+    <mergeCell ref="J55:J59"/>
+    <mergeCell ref="F60:F64"/>
+    <mergeCell ref="G60:G64"/>
+    <mergeCell ref="J60:J64"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="J65:J66"/>
     <mergeCell ref="A67:A99"/>
     <mergeCell ref="D67:D99"/>
     <mergeCell ref="E67:E99"/>
@@ -4780,72 +4848,28 @@
     <mergeCell ref="F89:F91"/>
     <mergeCell ref="G89:G91"/>
     <mergeCell ref="J89:J91"/>
-    <mergeCell ref="F49:F51"/>
-    <mergeCell ref="G49:G51"/>
-    <mergeCell ref="J49:J51"/>
-    <mergeCell ref="F52:F54"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="J52:J54"/>
-    <mergeCell ref="A55:A66"/>
-    <mergeCell ref="D55:D66"/>
-    <mergeCell ref="E55:E66"/>
-    <mergeCell ref="F55:F59"/>
-    <mergeCell ref="G55:G59"/>
-    <mergeCell ref="J55:J59"/>
-    <mergeCell ref="F60:F64"/>
-    <mergeCell ref="G60:G64"/>
-    <mergeCell ref="J60:J64"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="J65:J66"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="A34:A54"/>
-    <mergeCell ref="D34:D54"/>
-    <mergeCell ref="E34:E54"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="J34:J36"/>
-    <mergeCell ref="F37:F39"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="J37:J39"/>
-    <mergeCell ref="F40:F42"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="J40:J42"/>
-    <mergeCell ref="F43:F45"/>
-    <mergeCell ref="G43:G45"/>
-    <mergeCell ref="J43:J45"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="G46:G48"/>
-    <mergeCell ref="J46:J48"/>
-    <mergeCell ref="A2:A33"/>
-    <mergeCell ref="D2:D33"/>
-    <mergeCell ref="E2:E33"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="J2:J5"/>
-    <mergeCell ref="F6:F10"/>
-    <mergeCell ref="G6:G10"/>
-    <mergeCell ref="J6:J10"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="G11:G14"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="F15:F19"/>
-    <mergeCell ref="G15:G19"/>
-    <mergeCell ref="J15:J19"/>
-    <mergeCell ref="F20:F24"/>
-    <mergeCell ref="G20:G24"/>
-    <mergeCell ref="J20:J24"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="J25:J27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="F92:F94"/>
+    <mergeCell ref="G92:G94"/>
+    <mergeCell ref="J92:J94"/>
+    <mergeCell ref="F95:F97"/>
+    <mergeCell ref="G95:G97"/>
+    <mergeCell ref="J95:J97"/>
+    <mergeCell ref="F98:F99"/>
+    <mergeCell ref="G98:G99"/>
+    <mergeCell ref="J98:J99"/>
+    <mergeCell ref="A111:I111"/>
+    <mergeCell ref="A100:A110"/>
+    <mergeCell ref="D100:D110"/>
+    <mergeCell ref="E100:E110"/>
+    <mergeCell ref="F101:F103"/>
+    <mergeCell ref="G101:G103"/>
+    <mergeCell ref="J101:J103"/>
+    <mergeCell ref="F104:F107"/>
+    <mergeCell ref="G104:G107"/>
+    <mergeCell ref="J104:J107"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="J108:J110"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4878,13 +4902,13 @@
       <c r="C1" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -4893,7 +4917,7 @@
       <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="17" t="s">
         <v>173</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -4901,25 +4925,25 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32">
+      <c r="B2" s="33">
         <v>46253</v>
       </c>
       <c r="C2" t="s">
         <v>175</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="24" t="s">
         <v>85</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -4928,68 +4952,68 @@
       <c r="I2" s="8">
         <v>14</v>
       </c>
-      <c r="J2" s="17">
+      <c r="J2" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A3" s="15"/>
+      <c r="A3" s="25"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
       <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I3" s="8">
         <v>14</v>
       </c>
-      <c r="J3" s="18"/>
+      <c r="J3" s="28"/>
     </row>
     <row r="4" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A4" s="15"/>
+      <c r="A4" s="25"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I4" s="8">
         <v>14</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A5" s="15"/>
+      <c r="A5" s="25"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
       <c r="H5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I5" s="8">
         <v>9</v>
       </c>
-      <c r="J5" s="19"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A6" s="15"/>
+      <c r="A6" s="25"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="14" t="s">
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="24" t="s">
         <v>87</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -4998,84 +5022,84 @@
       <c r="I6" s="8">
         <v>5</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="27">
         <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A7" s="15"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I7" s="8">
         <v>14</v>
       </c>
-      <c r="J7" s="18"/>
+      <c r="J7" s="28"/>
     </row>
     <row r="8" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A8" s="15"/>
+      <c r="A8" s="25"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="8">
         <v>14</v>
       </c>
-      <c r="J8" s="18"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A9" s="15"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I9" s="8">
         <v>14</v>
       </c>
-      <c r="J9" s="18"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A10" s="15"/>
+      <c r="A10" s="25"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="8">
         <v>3</v>
       </c>
-      <c r="J10" s="19"/>
+      <c r="J10" s="29"/>
     </row>
     <row r="11" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A11" s="15"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="14" t="s">
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="24" t="s">
         <v>88</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -5084,68 +5108,68 @@
       <c r="I11" s="8">
         <v>11</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A12" s="15"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I12" s="8">
         <v>14</v>
       </c>
-      <c r="J12" s="18"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A13" s="15"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="4" t="s">
         <v>19</v>
       </c>
       <c r="I13" s="8">
         <v>14</v>
       </c>
-      <c r="J13" s="18"/>
+      <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A14" s="15"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I14" s="8">
         <v>12</v>
       </c>
-      <c r="J14" s="19"/>
+      <c r="J14" s="29"/>
     </row>
     <row r="15" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A15" s="15"/>
+      <c r="A15" s="25"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="14" t="s">
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="24" t="s">
         <v>90</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -5154,84 +5178,84 @@
       <c r="I15" s="8">
         <v>2</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A16" s="15"/>
+      <c r="A16" s="25"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
       <c r="H16" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="8">
         <v>14</v>
       </c>
-      <c r="J16" s="18"/>
+      <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A17" s="15"/>
+      <c r="A17" s="25"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I17" s="8">
         <v>14</v>
       </c>
-      <c r="J17" s="18"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A18" s="15"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
       <c r="H18" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I18" s="8">
         <v>14</v>
       </c>
-      <c r="J18" s="18"/>
+      <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A19" s="15"/>
+      <c r="A19" s="25"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
       <c r="H19" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I19" s="8">
         <v>7</v>
       </c>
-      <c r="J19" s="19"/>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A20" s="15"/>
+      <c r="A20" s="25"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="14" t="s">
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="24" t="s">
         <v>92</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -5240,84 +5264,84 @@
       <c r="I20" s="8">
         <v>7</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A21" s="15"/>
+      <c r="A21" s="25"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
       <c r="H21" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I21" s="8">
         <v>14</v>
       </c>
-      <c r="J21" s="18"/>
+      <c r="J21" s="28"/>
     </row>
     <row r="22" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A22" s="15"/>
+      <c r="A22" s="25"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
       <c r="H22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I22" s="8">
         <v>14</v>
       </c>
-      <c r="J22" s="18"/>
+      <c r="J22" s="28"/>
     </row>
     <row r="23" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A23" s="15"/>
+      <c r="A23" s="25"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
       <c r="H23" s="4" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="8">
         <v>14</v>
       </c>
-      <c r="J23" s="18"/>
+      <c r="J23" s="28"/>
     </row>
     <row r="24" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A24" s="15"/>
+      <c r="A24" s="25"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
       <c r="H24" s="4" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="8">
         <v>2</v>
       </c>
-      <c r="J24" s="19"/>
+      <c r="J24" s="29"/>
     </row>
     <row r="25" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A25" s="15"/>
+      <c r="A25" s="25"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="14" t="s">
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="24" t="s">
         <v>94</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -5326,52 +5350,52 @@
       <c r="I25" s="8">
         <v>12</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A26" s="15"/>
+      <c r="A26" s="25"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
       <c r="H26" s="4" t="s">
         <v>34</v>
       </c>
       <c r="I26" s="8">
         <v>14</v>
       </c>
-      <c r="J26" s="18"/>
+      <c r="J26" s="28"/>
     </row>
     <row r="27" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A27" s="15"/>
+      <c r="A27" s="25"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
       <c r="H27" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I27" s="8">
         <v>25</v>
       </c>
-      <c r="J27" s="19"/>
+      <c r="J27" s="29"/>
     </row>
     <row r="28" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A28" s="15"/>
+      <c r="A28" s="25"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="14" t="s">
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="G28" s="24" t="s">
         <v>96</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -5380,36 +5404,36 @@
       <c r="I28" s="8">
         <v>15</v>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="27">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A29" s="15"/>
+      <c r="A29" s="25"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
       <c r="H29" s="4" t="s">
         <v>37</v>
       </c>
       <c r="I29" s="8">
         <v>35</v>
       </c>
-      <c r="J29" s="19"/>
+      <c r="J29" s="29"/>
     </row>
     <row r="30" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A30" s="15"/>
+      <c r="A30" s="25"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="14" t="s">
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="G30" s="24" t="s">
         <v>97</v>
       </c>
       <c r="H30" s="4" t="s">
@@ -5418,48 +5442,48 @@
       <c r="I30" s="8">
         <v>1</v>
       </c>
-      <c r="J30" s="17">
+      <c r="J30" s="27">
         <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A31" s="15"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
       <c r="H31" s="8">
         <v>208</v>
       </c>
       <c r="I31" s="8">
         <v>27</v>
       </c>
-      <c r="J31" s="18"/>
+      <c r="J31" s="28"/>
     </row>
     <row r="32" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A32" s="15"/>
+      <c r="A32" s="25"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="8">
         <v>213</v>
       </c>
       <c r="I32" s="8">
         <v>22</v>
       </c>
-      <c r="J32" s="19"/>
+      <c r="J32" s="29"/>
     </row>
     <row r="33" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A33" s="16"/>
+      <c r="A33" s="26"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
       <c r="F33" s="4" t="s">
         <v>93</v>
       </c>
@@ -5489,63 +5513,63 @@
       <c r="J34" s="12"/>
     </row>
     <row r="35" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A35" s="20"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
       <c r="H35" s="8">
         <v>216</v>
       </c>
       <c r="I35" s="8">
         <v>24</v>
       </c>
-      <c r="J35" s="20"/>
+      <c r="J35" s="21"/>
     </row>
     <row r="36" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A36" s="21"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
       <c r="H36" s="8">
         <v>217</v>
       </c>
       <c r="I36" s="8">
         <v>24</v>
       </c>
-      <c r="J36" s="21"/>
+      <c r="J36" s="22"/>
     </row>
     <row r="37" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A37" s="21"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
       <c r="H37" s="8">
         <v>218</v>
       </c>
       <c r="I37" s="8">
         <v>1</v>
       </c>
-      <c r="J37" s="22"/>
+      <c r="J37" s="23"/>
     </row>
     <row r="38" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A38" s="21"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="14" t="s">
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="G38" s="14" t="s">
+      <c r="G38" s="24" t="s">
         <v>100</v>
       </c>
       <c r="H38" s="8">
@@ -5554,52 +5578,52 @@
       <c r="I38" s="8">
         <v>23</v>
       </c>
-      <c r="J38" s="17">
+      <c r="J38" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A39" s="21"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
       <c r="H39" s="8">
         <v>219</v>
       </c>
       <c r="I39" s="8">
         <v>24</v>
       </c>
-      <c r="J39" s="18"/>
+      <c r="J39" s="28"/>
     </row>
     <row r="40" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A40" s="21"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
       <c r="H40" s="8">
         <v>220</v>
       </c>
       <c r="I40" s="8">
         <v>4</v>
       </c>
-      <c r="J40" s="19"/>
+      <c r="J40" s="29"/>
     </row>
     <row r="41" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A41" s="21"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="14" t="s">
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="G41" s="14" t="s">
+      <c r="G41" s="24" t="s">
         <v>101</v>
       </c>
       <c r="H41" s="8">
@@ -5608,52 +5632,52 @@
       <c r="I41" s="8">
         <v>20</v>
       </c>
-      <c r="J41" s="17">
+      <c r="J41" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A42" s="21"/>
+      <c r="A42" s="22"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
       <c r="H42" s="8">
         <v>221</v>
       </c>
       <c r="I42" s="8">
         <v>24</v>
       </c>
-      <c r="J42" s="18"/>
+      <c r="J42" s="28"/>
     </row>
     <row r="43" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A43" s="21"/>
+      <c r="A43" s="22"/>
       <c r="B43" s="10"/>
       <c r="C43" s="10"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
       <c r="H43" s="8">
         <v>222</v>
       </c>
       <c r="I43" s="8">
         <v>7</v>
       </c>
-      <c r="J43" s="19"/>
+      <c r="J43" s="29"/>
     </row>
     <row r="44" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A44" s="21"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="10"/>
       <c r="C44" s="10"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="14" t="s">
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="G44" s="14" t="s">
+      <c r="G44" s="24" t="s">
         <v>102</v>
       </c>
       <c r="H44" s="8">
@@ -5662,52 +5686,52 @@
       <c r="I44" s="8">
         <v>17</v>
       </c>
-      <c r="J44" s="17">
+      <c r="J44" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A45" s="21"/>
+      <c r="A45" s="22"/>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
       <c r="H45" s="8">
         <v>223</v>
       </c>
       <c r="I45" s="8">
         <v>24</v>
       </c>
-      <c r="J45" s="18"/>
+      <c r="J45" s="28"/>
     </row>
     <row r="46" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A46" s="21"/>
+      <c r="A46" s="22"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
       <c r="H46" s="8">
         <v>224</v>
       </c>
       <c r="I46" s="8">
         <v>10</v>
       </c>
-      <c r="J46" s="19"/>
+      <c r="J46" s="29"/>
     </row>
     <row r="47" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A47" s="21"/>
+      <c r="A47" s="22"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="14" t="s">
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="G47" s="14" t="s">
+      <c r="G47" s="24" t="s">
         <v>104</v>
       </c>
       <c r="H47" s="8">
@@ -5716,52 +5740,52 @@
       <c r="I47" s="8">
         <v>14</v>
       </c>
-      <c r="J47" s="17">
+      <c r="J47" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A48" s="21"/>
+      <c r="A48" s="22"/>
       <c r="B48" s="10"/>
       <c r="C48" s="10"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
       <c r="H48" s="8">
         <v>303</v>
       </c>
       <c r="I48" s="8">
         <v>24</v>
       </c>
-      <c r="J48" s="18"/>
+      <c r="J48" s="28"/>
     </row>
     <row r="49" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A49" s="21"/>
+      <c r="A49" s="22"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
       <c r="H49" s="8">
         <v>304</v>
       </c>
       <c r="I49" s="8">
         <v>13</v>
       </c>
-      <c r="J49" s="19"/>
+      <c r="J49" s="29"/>
     </row>
     <row r="50" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A50" s="21"/>
+      <c r="A50" s="22"/>
       <c r="B50" s="10"/>
       <c r="C50" s="10"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="14" t="s">
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="G50" s="14" t="s">
+      <c r="G50" s="24" t="s">
         <v>105</v>
       </c>
       <c r="H50" s="8">
@@ -5770,52 +5794,52 @@
       <c r="I50" s="8">
         <v>11</v>
       </c>
-      <c r="J50" s="17">
+      <c r="J50" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A51" s="21"/>
+      <c r="A51" s="22"/>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
       <c r="H51" s="8">
         <v>305</v>
       </c>
       <c r="I51" s="8">
         <v>24</v>
       </c>
-      <c r="J51" s="18"/>
+      <c r="J51" s="28"/>
     </row>
     <row r="52" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A52" s="21"/>
+      <c r="A52" s="22"/>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
       <c r="H52" s="8">
         <v>306</v>
       </c>
       <c r="I52" s="8">
         <v>16</v>
       </c>
-      <c r="J52" s="19"/>
+      <c r="J52" s="29"/>
     </row>
     <row r="53" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A53" s="21"/>
+      <c r="A53" s="22"/>
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="14" t="s">
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="G53" s="14" t="s">
+      <c r="G53" s="24" t="s">
         <v>106</v>
       </c>
       <c r="H53" s="8">
@@ -5824,52 +5848,52 @@
       <c r="I53" s="8">
         <v>8</v>
       </c>
-      <c r="J53" s="17">
+      <c r="J53" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A54" s="21"/>
+      <c r="A54" s="22"/>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25"/>
       <c r="H54" s="8">
         <v>307</v>
       </c>
       <c r="I54" s="8">
         <v>28</v>
       </c>
-      <c r="J54" s="18"/>
+      <c r="J54" s="28"/>
     </row>
     <row r="55" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A55" s="21"/>
+      <c r="A55" s="22"/>
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
       <c r="H55" s="4" t="s">
         <v>53</v>
       </c>
       <c r="I55" s="8">
         <v>15</v>
       </c>
-      <c r="J55" s="19"/>
+      <c r="J55" s="29"/>
     </row>
     <row r="56" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A56" s="21"/>
+      <c r="A56" s="22"/>
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="14" t="s">
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="G56" s="14" t="s">
+      <c r="G56" s="24" t="s">
         <v>108</v>
       </c>
       <c r="H56" s="4" t="s">
@@ -5878,52 +5902,52 @@
       <c r="I56" s="8">
         <v>9</v>
       </c>
-      <c r="J56" s="17">
+      <c r="J56" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A57" s="21"/>
+      <c r="A57" s="22"/>
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
       <c r="H57" s="4" t="s">
         <v>55</v>
       </c>
       <c r="I57" s="8">
         <v>24</v>
       </c>
-      <c r="J57" s="18"/>
+      <c r="J57" s="28"/>
     </row>
     <row r="58" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A58" s="21"/>
+      <c r="A58" s="22"/>
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
       <c r="H58" s="8">
         <v>320</v>
       </c>
       <c r="I58" s="8">
         <v>18</v>
       </c>
-      <c r="J58" s="19"/>
+      <c r="J58" s="29"/>
     </row>
     <row r="59" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A59" s="21"/>
+      <c r="A59" s="22"/>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="14" t="s">
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="G59" s="14" t="s">
+      <c r="G59" s="24" t="s">
         <v>109</v>
       </c>
       <c r="H59" s="8">
@@ -5932,36 +5956,36 @@
       <c r="I59" s="8">
         <v>29</v>
       </c>
-      <c r="J59" s="17">
+      <c r="J59" s="27">
         <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A60" s="21"/>
+      <c r="A60" s="22"/>
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
       <c r="H60" s="4" t="s">
         <v>110</v>
       </c>
       <c r="I60" s="8">
         <v>21</v>
       </c>
-      <c r="J60" s="19"/>
+      <c r="J60" s="29"/>
     </row>
     <row r="61" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A61" s="21"/>
+      <c r="A61" s="22"/>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="14" t="s">
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="G61" s="14" t="s">
+      <c r="G61" s="24" t="s">
         <v>112</v>
       </c>
       <c r="H61" s="4" t="s">
@@ -5970,52 +5994,52 @@
       <c r="I61" s="8">
         <v>4</v>
       </c>
-      <c r="J61" s="17">
+      <c r="J61" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A62" s="21"/>
+      <c r="A62" s="22"/>
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
       <c r="H62" s="4" t="s">
         <v>113</v>
       </c>
       <c r="I62" s="8">
         <v>25</v>
       </c>
-      <c r="J62" s="18"/>
+      <c r="J62" s="28"/>
     </row>
     <row r="63" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A63" s="21"/>
+      <c r="A63" s="22"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
       <c r="H63" s="4" t="s">
         <v>114</v>
       </c>
       <c r="I63" s="8">
         <v>22</v>
       </c>
-      <c r="J63" s="19"/>
+      <c r="J63" s="29"/>
     </row>
     <row r="64" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A64" s="21"/>
+      <c r="A64" s="22"/>
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="14" t="s">
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="G64" s="14" t="s">
+      <c r="G64" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H64" s="4" t="s">
@@ -6024,48 +6048,48 @@
       <c r="I64" s="8">
         <v>3</v>
       </c>
-      <c r="J64" s="17">
+      <c r="J64" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A65" s="21"/>
+      <c r="A65" s="22"/>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="25"/>
       <c r="H65" s="4" t="s">
         <v>117</v>
       </c>
       <c r="I65" s="8">
         <v>25</v>
       </c>
-      <c r="J65" s="18"/>
+      <c r="J65" s="28"/>
     </row>
     <row r="66" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A66" s="21"/>
+      <c r="A66" s="22"/>
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
       <c r="H66" s="4" t="s">
         <v>118</v>
       </c>
       <c r="I66" s="8">
         <v>23</v>
       </c>
-      <c r="J66" s="19"/>
+      <c r="J66" s="29"/>
     </row>
     <row r="67" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A67" s="22"/>
+      <c r="A67" s="23"/>
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
+      <c r="D67" s="23"/>
+      <c r="E67" s="23"/>
       <c r="F67" s="4" t="s">
         <v>115</v>
       </c>
@@ -6083,47 +6107,47 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A68" s="20"/>
+      <c r="A68" s="21"/>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
       <c r="H68" s="4" t="s">
         <v>120</v>
       </c>
       <c r="I68" s="8">
         <v>25</v>
       </c>
-      <c r="J68" s="26"/>
+      <c r="J68" s="30"/>
     </row>
     <row r="69" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A69" s="21"/>
+      <c r="A69" s="22"/>
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="27"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
       <c r="H69" s="8">
         <v>514</v>
       </c>
       <c r="I69" s="8">
         <v>24</v>
       </c>
-      <c r="J69" s="27"/>
+      <c r="J69" s="31"/>
     </row>
     <row r="70" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A70" s="21"/>
+      <c r="A70" s="22"/>
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="14" t="s">
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="G70" s="14" t="s">
+      <c r="G70" s="24" t="s">
         <v>122</v>
       </c>
       <c r="H70" s="8">
@@ -6132,52 +6156,52 @@
       <c r="I70" s="8">
         <v>24</v>
       </c>
-      <c r="J70" s="17">
+      <c r="J70" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A71" s="21"/>
+      <c r="A71" s="22"/>
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
       <c r="H71" s="8">
         <v>516</v>
       </c>
       <c r="I71" s="8">
         <v>24</v>
       </c>
-      <c r="J71" s="18"/>
+      <c r="J71" s="28"/>
     </row>
     <row r="72" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A72" s="21"/>
+      <c r="A72" s="22"/>
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="16"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
       <c r="H72" s="4" t="s">
         <v>123</v>
       </c>
       <c r="I72" s="8">
         <v>3</v>
       </c>
-      <c r="J72" s="19"/>
+      <c r="J72" s="29"/>
     </row>
     <row r="73" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A73" s="21"/>
+      <c r="A73" s="22"/>
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="14" t="s">
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="G73" s="14" t="s">
+      <c r="G73" s="24" t="s">
         <v>124</v>
       </c>
       <c r="H73" s="4" t="s">
@@ -6186,42 +6210,42 @@
       <c r="I73" s="8">
         <v>21</v>
       </c>
-      <c r="J73" s="17">
+      <c r="J73" s="27">
         <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A74" s="22"/>
+      <c r="A74" s="23"/>
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
-      <c r="D74" s="22"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="16"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
       <c r="H74" s="8">
         <v>518</v>
       </c>
       <c r="I74" s="8">
         <v>29</v>
       </c>
-      <c r="J74" s="19"/>
+      <c r="J74" s="29"/>
     </row>
     <row r="75" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="24" t="s">
         <v>3</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
-      <c r="D75" s="14" t="s">
+      <c r="D75" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="E75" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="F75" s="14" t="s">
+      <c r="F75" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="G75" s="14" t="s">
+      <c r="G75" s="24" t="s">
         <v>128</v>
       </c>
       <c r="H75" s="4" t="s">
@@ -6230,84 +6254,84 @@
       <c r="I75" s="8">
         <v>11</v>
       </c>
-      <c r="J75" s="17">
+      <c r="J75" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A76" s="15"/>
+      <c r="A76" s="25"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="15"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
       <c r="H76" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I76" s="8">
         <v>11</v>
       </c>
-      <c r="J76" s="18"/>
+      <c r="J76" s="28"/>
     </row>
     <row r="77" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A77" s="15"/>
+      <c r="A77" s="25"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
+      <c r="D77" s="25"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
       <c r="H77" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I77" s="8">
         <v>11</v>
       </c>
-      <c r="J77" s="18"/>
+      <c r="J77" s="28"/>
     </row>
     <row r="78" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A78" s="15"/>
+      <c r="A78" s="25"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="15"/>
+      <c r="D78" s="25"/>
+      <c r="E78" s="25"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
       <c r="H78" s="4" t="s">
         <v>11</v>
       </c>
       <c r="I78" s="8">
         <v>11</v>
       </c>
-      <c r="J78" s="18"/>
+      <c r="J78" s="28"/>
     </row>
     <row r="79" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A79" s="15"/>
+      <c r="A79" s="25"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="25"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
       <c r="H79" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I79" s="8">
         <v>7</v>
       </c>
-      <c r="J79" s="19"/>
+      <c r="J79" s="29"/>
     </row>
     <row r="80" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A80" s="15"/>
+      <c r="A80" s="25"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="14" t="s">
+      <c r="D80" s="25"/>
+      <c r="E80" s="25"/>
+      <c r="F80" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="G80" s="14" t="s">
+      <c r="G80" s="24" t="s">
         <v>129</v>
       </c>
       <c r="H80" s="4" t="s">
@@ -6316,84 +6340,84 @@
       <c r="I80" s="8">
         <v>4</v>
       </c>
-      <c r="J80" s="17">
+      <c r="J80" s="27">
         <v>43</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A81" s="15"/>
+      <c r="A81" s="25"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
-      <c r="D81" s="15"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="15"/>
-      <c r="G81" s="15"/>
+      <c r="D81" s="25"/>
+      <c r="E81" s="25"/>
+      <c r="F81" s="25"/>
+      <c r="G81" s="25"/>
       <c r="H81" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I81" s="8">
         <v>11</v>
       </c>
-      <c r="J81" s="18"/>
+      <c r="J81" s="28"/>
     </row>
     <row r="82" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A82" s="15"/>
+      <c r="A82" s="25"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15"/>
+      <c r="D82" s="25"/>
+      <c r="E82" s="25"/>
+      <c r="F82" s="25"/>
+      <c r="G82" s="25"/>
       <c r="H82" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="8">
         <v>11</v>
       </c>
-      <c r="J82" s="18"/>
+      <c r="J82" s="28"/>
     </row>
     <row r="83" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A83" s="15"/>
+      <c r="A83" s="25"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="15"/>
-      <c r="G83" s="15"/>
+      <c r="D83" s="25"/>
+      <c r="E83" s="25"/>
+      <c r="F83" s="25"/>
+      <c r="G83" s="25"/>
       <c r="H83" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I83" s="8">
         <v>11</v>
       </c>
-      <c r="J83" s="18"/>
+      <c r="J83" s="28"/>
     </row>
     <row r="84" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A84" s="15"/>
+      <c r="A84" s="25"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="15"/>
-      <c r="F84" s="16"/>
-      <c r="G84" s="16"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="26"/>
+      <c r="G84" s="26"/>
       <c r="H84" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I84" s="8">
         <v>6</v>
       </c>
-      <c r="J84" s="19"/>
+      <c r="J84" s="29"/>
     </row>
     <row r="85" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A85" s="15"/>
+      <c r="A85" s="25"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
-      <c r="D85" s="15"/>
-      <c r="E85" s="15"/>
-      <c r="F85" s="14" t="s">
+      <c r="D85" s="25"/>
+      <c r="E85" s="25"/>
+      <c r="F85" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="G85" s="14" t="s">
+      <c r="G85" s="24" t="s">
         <v>131</v>
       </c>
       <c r="H85" s="4" t="s">
@@ -6402,100 +6426,100 @@
       <c r="I85" s="8">
         <v>5</v>
       </c>
-      <c r="J85" s="17">
+      <c r="J85" s="27">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A86" s="15"/>
+      <c r="A86" s="25"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
-      <c r="D86" s="15"/>
-      <c r="E86" s="15"/>
-      <c r="F86" s="15"/>
-      <c r="G86" s="15"/>
+      <c r="D86" s="25"/>
+      <c r="E86" s="25"/>
+      <c r="F86" s="25"/>
+      <c r="G86" s="25"/>
       <c r="H86" s="4" t="s">
         <v>19</v>
       </c>
       <c r="I86" s="8">
         <v>11</v>
       </c>
-      <c r="J86" s="18"/>
+      <c r="J86" s="28"/>
     </row>
     <row r="87" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A87" s="15"/>
+      <c r="A87" s="25"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
-      <c r="D87" s="15"/>
-      <c r="E87" s="15"/>
-      <c r="F87" s="15"/>
-      <c r="G87" s="15"/>
+      <c r="D87" s="25"/>
+      <c r="E87" s="25"/>
+      <c r="F87" s="25"/>
+      <c r="G87" s="25"/>
       <c r="H87" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I87" s="8">
         <v>11</v>
       </c>
-      <c r="J87" s="18"/>
+      <c r="J87" s="28"/>
     </row>
     <row r="88" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A88" s="15"/>
+      <c r="A88" s="25"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
-      <c r="D88" s="15"/>
-      <c r="E88" s="15"/>
-      <c r="F88" s="15"/>
-      <c r="G88" s="15"/>
+      <c r="D88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
       <c r="H88" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I88" s="8">
         <v>11</v>
       </c>
-      <c r="J88" s="18"/>
+      <c r="J88" s="28"/>
     </row>
     <row r="89" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A89" s="15"/>
+      <c r="A89" s="25"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
-      <c r="D89" s="15"/>
-      <c r="E89" s="15"/>
-      <c r="F89" s="15"/>
-      <c r="G89" s="15"/>
+      <c r="D89" s="25"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="25"/>
+      <c r="G89" s="25"/>
       <c r="H89" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I89" s="8">
         <v>11</v>
       </c>
-      <c r="J89" s="18"/>
+      <c r="J89" s="28"/>
     </row>
     <row r="90" spans="1:10" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="15"/>
+      <c r="A90" s="25"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
-      <c r="D90" s="15"/>
-      <c r="E90" s="15"/>
-      <c r="F90" s="16"/>
-      <c r="G90" s="16"/>
+      <c r="D90" s="25"/>
+      <c r="E90" s="25"/>
+      <c r="F90" s="26"/>
+      <c r="G90" s="26"/>
       <c r="H90" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I90" s="8">
         <v>1</v>
       </c>
-      <c r="J90" s="19"/>
+      <c r="J90" s="29"/>
     </row>
     <row r="91" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A91" s="15"/>
+      <c r="A91" s="25"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
-      <c r="D91" s="15"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="14" t="s">
+      <c r="D91" s="25"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="G91" s="14" t="s">
+      <c r="G91" s="24" t="s">
         <v>132</v>
       </c>
       <c r="H91" s="4" t="s">
@@ -6504,84 +6528,84 @@
       <c r="I91" s="8">
         <v>10</v>
       </c>
-      <c r="J91" s="17">
+      <c r="J91" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A92" s="15"/>
+      <c r="A92" s="25"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
+      <c r="D92" s="25"/>
+      <c r="E92" s="25"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="25"/>
       <c r="H92" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I92" s="8">
         <v>11</v>
       </c>
-      <c r="J92" s="18"/>
+      <c r="J92" s="28"/>
     </row>
     <row r="93" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A93" s="15"/>
+      <c r="A93" s="25"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15"/>
+      <c r="D93" s="25"/>
+      <c r="E93" s="25"/>
+      <c r="F93" s="25"/>
+      <c r="G93" s="25"/>
       <c r="H93" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I93" s="8">
         <v>11</v>
       </c>
-      <c r="J93" s="18"/>
+      <c r="J93" s="28"/>
     </row>
     <row r="94" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A94" s="15"/>
+      <c r="A94" s="25"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
-      <c r="D94" s="15"/>
-      <c r="E94" s="15"/>
-      <c r="F94" s="15"/>
-      <c r="G94" s="15"/>
+      <c r="D94" s="25"/>
+      <c r="E94" s="25"/>
+      <c r="F94" s="25"/>
+      <c r="G94" s="25"/>
       <c r="H94" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I94" s="8">
         <v>11</v>
       </c>
-      <c r="J94" s="18"/>
+      <c r="J94" s="28"/>
     </row>
     <row r="95" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A95" s="15"/>
+      <c r="A95" s="25"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
-      <c r="D95" s="15"/>
-      <c r="E95" s="15"/>
-      <c r="F95" s="16"/>
-      <c r="G95" s="16"/>
+      <c r="D95" s="25"/>
+      <c r="E95" s="25"/>
+      <c r="F95" s="26"/>
+      <c r="G95" s="26"/>
       <c r="H95" s="4" t="s">
         <v>30</v>
       </c>
       <c r="I95" s="8">
         <v>8</v>
       </c>
-      <c r="J95" s="19"/>
+      <c r="J95" s="29"/>
     </row>
     <row r="96" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A96" s="15"/>
+      <c r="A96" s="25"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
-      <c r="D96" s="15"/>
-      <c r="E96" s="15"/>
-      <c r="F96" s="14" t="s">
+      <c r="D96" s="25"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="G96" s="14" t="s">
+      <c r="G96" s="24" t="s">
         <v>134</v>
       </c>
       <c r="H96" s="4" t="s">
@@ -6590,64 +6614,64 @@
       <c r="I96" s="8">
         <v>3</v>
       </c>
-      <c r="J96" s="17">
+      <c r="J96" s="27">
         <v>49</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A97" s="15"/>
+      <c r="A97" s="25"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="15"/>
-      <c r="F97" s="15"/>
-      <c r="G97" s="15"/>
+      <c r="D97" s="25"/>
+      <c r="E97" s="25"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25"/>
       <c r="H97" s="4" t="s">
         <v>31</v>
       </c>
       <c r="I97" s="8">
         <v>11</v>
       </c>
-      <c r="J97" s="18"/>
+      <c r="J97" s="28"/>
     </row>
     <row r="98" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A98" s="15"/>
+      <c r="A98" s="25"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
-      <c r="D98" s="15"/>
-      <c r="E98" s="15"/>
-      <c r="F98" s="15"/>
-      <c r="G98" s="15"/>
+      <c r="D98" s="25"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="25"/>
       <c r="H98" s="4" t="s">
         <v>34</v>
       </c>
       <c r="I98" s="8">
         <v>11</v>
       </c>
-      <c r="J98" s="18"/>
+      <c r="J98" s="28"/>
     </row>
     <row r="99" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A99" s="15"/>
+      <c r="A99" s="25"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
-      <c r="D99" s="15"/>
-      <c r="E99" s="15"/>
-      <c r="F99" s="16"/>
-      <c r="G99" s="16"/>
+      <c r="D99" s="25"/>
+      <c r="E99" s="25"/>
+      <c r="F99" s="26"/>
+      <c r="G99" s="26"/>
       <c r="H99" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I99" s="8">
         <v>24</v>
       </c>
-      <c r="J99" s="19"/>
+      <c r="J99" s="29"/>
     </row>
     <row r="100" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A100" s="16"/>
+      <c r="A100" s="26"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
-      <c r="D100" s="16"/>
-      <c r="E100" s="16"/>
+      <c r="D100" s="26"/>
+      <c r="E100" s="26"/>
       <c r="F100" s="4" t="s">
         <v>133</v>
       </c>
@@ -6666,47 +6690,47 @@
     </row>
     <row r="101" spans="1:10" ht="0.95" customHeight="1"/>
     <row r="102" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A102" s="20"/>
+      <c r="A102" s="21"/>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
-      <c r="D102" s="20"/>
-      <c r="E102" s="20"/>
-      <c r="F102" s="26"/>
-      <c r="G102" s="26"/>
+      <c r="D102" s="21"/>
+      <c r="E102" s="21"/>
+      <c r="F102" s="30"/>
+      <c r="G102" s="30"/>
       <c r="H102" s="4" t="s">
         <v>37</v>
       </c>
       <c r="I102" s="8">
         <v>36</v>
       </c>
-      <c r="J102" s="26"/>
+      <c r="J102" s="30"/>
     </row>
     <row r="103" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A103" s="21"/>
+      <c r="A103" s="22"/>
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
-      <c r="D103" s="21"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="27"/>
-      <c r="G103" s="27"/>
+      <c r="D103" s="22"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="31"/>
+      <c r="G103" s="31"/>
       <c r="H103" s="8">
         <v>208</v>
       </c>
       <c r="I103" s="8">
         <v>5</v>
       </c>
-      <c r="J103" s="27"/>
+      <c r="J103" s="31"/>
     </row>
     <row r="104" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A104" s="21"/>
+      <c r="A104" s="22"/>
       <c r="B104" s="10"/>
       <c r="C104" s="10"/>
-      <c r="D104" s="21"/>
-      <c r="E104" s="21"/>
-      <c r="F104" s="14" t="s">
+      <c r="D104" s="22"/>
+      <c r="E104" s="22"/>
+      <c r="F104" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="G104" s="14" t="s">
+      <c r="G104" s="24" t="s">
         <v>137</v>
       </c>
       <c r="H104" s="8">
@@ -6715,52 +6739,52 @@
       <c r="I104" s="8">
         <v>13</v>
       </c>
-      <c r="J104" s="17">
+      <c r="J104" s="27">
         <v>47</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A105" s="21"/>
+      <c r="A105" s="22"/>
       <c r="B105" s="10"/>
       <c r="C105" s="10"/>
-      <c r="D105" s="21"/>
-      <c r="E105" s="21"/>
-      <c r="F105" s="15"/>
-      <c r="G105" s="15"/>
+      <c r="D105" s="22"/>
+      <c r="E105" s="22"/>
+      <c r="F105" s="25"/>
+      <c r="G105" s="25"/>
       <c r="H105" s="8">
         <v>213</v>
       </c>
       <c r="I105" s="8">
         <v>24</v>
       </c>
-      <c r="J105" s="18"/>
+      <c r="J105" s="28"/>
     </row>
     <row r="106" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A106" s="21"/>
+      <c r="A106" s="22"/>
       <c r="B106" s="10"/>
       <c r="C106" s="10"/>
-      <c r="D106" s="21"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="16"/>
-      <c r="G106" s="16"/>
+      <c r="D106" s="22"/>
+      <c r="E106" s="22"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="26"/>
       <c r="H106" s="8">
         <v>216</v>
       </c>
       <c r="I106" s="8">
         <v>10</v>
       </c>
-      <c r="J106" s="19"/>
+      <c r="J106" s="29"/>
     </row>
     <row r="107" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A107" s="21"/>
+      <c r="A107" s="22"/>
       <c r="B107" s="10"/>
       <c r="C107" s="10"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="21"/>
-      <c r="F107" s="14" t="s">
+      <c r="D107" s="22"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="G107" s="14" t="s">
+      <c r="G107" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H107" s="8">
@@ -6769,52 +6793,52 @@
       <c r="I107" s="8">
         <v>14</v>
       </c>
-      <c r="J107" s="17">
+      <c r="J107" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A108" s="21"/>
+      <c r="A108" s="22"/>
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
-      <c r="D108" s="21"/>
-      <c r="E108" s="21"/>
-      <c r="F108" s="15"/>
-      <c r="G108" s="15"/>
+      <c r="D108" s="22"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="25"/>
+      <c r="G108" s="25"/>
       <c r="H108" s="8">
         <v>217</v>
       </c>
       <c r="I108" s="8">
         <v>24</v>
       </c>
-      <c r="J108" s="18"/>
+      <c r="J108" s="28"/>
     </row>
     <row r="109" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A109" s="21"/>
+      <c r="A109" s="22"/>
       <c r="B109" s="10"/>
       <c r="C109" s="10"/>
-      <c r="D109" s="21"/>
-      <c r="E109" s="21"/>
-      <c r="F109" s="16"/>
-      <c r="G109" s="16"/>
+      <c r="D109" s="22"/>
+      <c r="E109" s="22"/>
+      <c r="F109" s="26"/>
+      <c r="G109" s="26"/>
       <c r="H109" s="8">
         <v>218</v>
       </c>
       <c r="I109" s="8">
         <v>13</v>
       </c>
-      <c r="J109" s="19"/>
+      <c r="J109" s="29"/>
     </row>
     <row r="110" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A110" s="21"/>
+      <c r="A110" s="22"/>
       <c r="B110" s="10"/>
       <c r="C110" s="10"/>
-      <c r="D110" s="21"/>
-      <c r="E110" s="21"/>
-      <c r="F110" s="14" t="s">
+      <c r="D110" s="22"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="G110" s="14" t="s">
+      <c r="G110" s="24" t="s">
         <v>140</v>
       </c>
       <c r="H110" s="8">
@@ -6823,52 +6847,52 @@
       <c r="I110" s="8">
         <v>11</v>
       </c>
-      <c r="J110" s="17">
+      <c r="J110" s="27">
         <v>50</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A111" s="21"/>
+      <c r="A111" s="22"/>
       <c r="B111" s="10"/>
       <c r="C111" s="10"/>
-      <c r="D111" s="21"/>
-      <c r="E111" s="21"/>
-      <c r="F111" s="15"/>
-      <c r="G111" s="15"/>
+      <c r="D111" s="22"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="25"/>
+      <c r="G111" s="25"/>
       <c r="H111" s="8">
         <v>219</v>
       </c>
       <c r="I111" s="8">
         <v>24</v>
       </c>
-      <c r="J111" s="18"/>
+      <c r="J111" s="28"/>
     </row>
     <row r="112" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A112" s="21"/>
+      <c r="A112" s="22"/>
       <c r="B112" s="10"/>
       <c r="C112" s="10"/>
-      <c r="D112" s="21"/>
-      <c r="E112" s="21"/>
-      <c r="F112" s="16"/>
-      <c r="G112" s="16"/>
+      <c r="D112" s="22"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="26"/>
+      <c r="G112" s="26"/>
       <c r="H112" s="8">
         <v>220</v>
       </c>
       <c r="I112" s="8">
         <v>15</v>
       </c>
-      <c r="J112" s="19"/>
+      <c r="J112" s="29"/>
     </row>
     <row r="113" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A113" s="21"/>
+      <c r="A113" s="22"/>
       <c r="B113" s="10"/>
       <c r="C113" s="10"/>
-      <c r="D113" s="21"/>
-      <c r="E113" s="21"/>
-      <c r="F113" s="14" t="s">
+      <c r="D113" s="22"/>
+      <c r="E113" s="22"/>
+      <c r="F113" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="G113" s="14" t="s">
+      <c r="G113" s="24" t="s">
         <v>141</v>
       </c>
       <c r="H113" s="8">
@@ -6877,52 +6901,52 @@
       <c r="I113" s="8">
         <v>9</v>
       </c>
-      <c r="J113" s="17">
+      <c r="J113" s="27">
         <v>47</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A114" s="21"/>
+      <c r="A114" s="22"/>
       <c r="B114" s="10"/>
       <c r="C114" s="10"/>
-      <c r="D114" s="21"/>
-      <c r="E114" s="21"/>
-      <c r="F114" s="15"/>
-      <c r="G114" s="15"/>
+      <c r="D114" s="22"/>
+      <c r="E114" s="22"/>
+      <c r="F114" s="25"/>
+      <c r="G114" s="25"/>
       <c r="H114" s="8">
         <v>221</v>
       </c>
       <c r="I114" s="8">
         <v>24</v>
       </c>
-      <c r="J114" s="18"/>
+      <c r="J114" s="28"/>
     </row>
     <row r="115" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A115" s="21"/>
+      <c r="A115" s="22"/>
       <c r="B115" s="10"/>
       <c r="C115" s="10"/>
-      <c r="D115" s="21"/>
-      <c r="E115" s="21"/>
-      <c r="F115" s="16"/>
-      <c r="G115" s="16"/>
+      <c r="D115" s="22"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26"/>
       <c r="H115" s="8">
         <v>222</v>
       </c>
       <c r="I115" s="8">
         <v>14</v>
       </c>
-      <c r="J115" s="19"/>
+      <c r="J115" s="29"/>
     </row>
     <row r="116" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A116" s="21"/>
+      <c r="A116" s="22"/>
       <c r="B116" s="10"/>
       <c r="C116" s="10"/>
-      <c r="D116" s="21"/>
-      <c r="E116" s="21"/>
-      <c r="F116" s="14" t="s">
+      <c r="D116" s="22"/>
+      <c r="E116" s="22"/>
+      <c r="F116" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="G116" s="14" t="s">
+      <c r="G116" s="24" t="s">
         <v>142</v>
       </c>
       <c r="H116" s="8">
@@ -6931,52 +6955,52 @@
       <c r="I116" s="8">
         <v>10</v>
       </c>
-      <c r="J116" s="17">
+      <c r="J116" s="27">
         <v>46</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A117" s="21"/>
+      <c r="A117" s="22"/>
       <c r="B117" s="10"/>
       <c r="C117" s="10"/>
-      <c r="D117" s="21"/>
-      <c r="E117" s="21"/>
-      <c r="F117" s="15"/>
-      <c r="G117" s="15"/>
+      <c r="D117" s="22"/>
+      <c r="E117" s="22"/>
+      <c r="F117" s="25"/>
+      <c r="G117" s="25"/>
       <c r="H117" s="8">
         <v>223</v>
       </c>
       <c r="I117" s="8">
         <v>24</v>
       </c>
-      <c r="J117" s="18"/>
+      <c r="J117" s="28"/>
     </row>
     <row r="118" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A118" s="21"/>
+      <c r="A118" s="22"/>
       <c r="B118" s="10"/>
       <c r="C118" s="10"/>
-      <c r="D118" s="21"/>
-      <c r="E118" s="21"/>
-      <c r="F118" s="16"/>
-      <c r="G118" s="16"/>
+      <c r="D118" s="22"/>
+      <c r="E118" s="22"/>
+      <c r="F118" s="26"/>
+      <c r="G118" s="26"/>
       <c r="H118" s="8">
         <v>224</v>
       </c>
       <c r="I118" s="8">
         <v>12</v>
       </c>
-      <c r="J118" s="19"/>
+      <c r="J118" s="29"/>
     </row>
     <row r="119" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A119" s="21"/>
+      <c r="A119" s="22"/>
       <c r="B119" s="10"/>
       <c r="C119" s="10"/>
-      <c r="D119" s="21"/>
-      <c r="E119" s="21"/>
-      <c r="F119" s="14" t="s">
+      <c r="D119" s="22"/>
+      <c r="E119" s="22"/>
+      <c r="F119" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="G119" s="14" t="s">
+      <c r="G119" s="24" t="s">
         <v>143</v>
       </c>
       <c r="H119" s="8">
@@ -6985,44 +7009,138 @@
       <c r="I119" s="8">
         <v>12</v>
       </c>
-      <c r="J119" s="17">
+      <c r="J119" s="27">
         <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A120" s="22"/>
+      <c r="A120" s="23"/>
       <c r="B120" s="11"/>
       <c r="C120" s="11"/>
-      <c r="D120" s="22"/>
-      <c r="E120" s="22"/>
-      <c r="F120" s="16"/>
-      <c r="G120" s="16"/>
+      <c r="D120" s="23"/>
+      <c r="E120" s="23"/>
+      <c r="F120" s="26"/>
+      <c r="G120" s="26"/>
       <c r="H120" s="8">
         <v>303</v>
       </c>
       <c r="I120" s="8">
         <v>14</v>
       </c>
-      <c r="J120" s="19"/>
+      <c r="J120" s="29"/>
     </row>
     <row r="121" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A121" s="23" t="s">
+      <c r="A121" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B121" s="24"/>
-      <c r="C121" s="24"/>
-      <c r="D121" s="24"/>
-      <c r="E121" s="24"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
-      <c r="H121" s="24"/>
-      <c r="I121" s="25"/>
+      <c r="B121" s="19"/>
+      <c r="C121" s="19"/>
+      <c r="D121" s="19"/>
+      <c r="E121" s="19"/>
+      <c r="F121" s="19"/>
+      <c r="G121" s="19"/>
+      <c r="H121" s="19"/>
+      <c r="I121" s="20"/>
       <c r="J121" s="8">
         <v>1677</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="118">
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="D2:D33"/>
+    <mergeCell ref="E2:E33"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="G2:G5"/>
+    <mergeCell ref="J2:J5"/>
+    <mergeCell ref="F6:F10"/>
+    <mergeCell ref="G6:G10"/>
+    <mergeCell ref="J6:J10"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="G11:G14"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="F15:F19"/>
+    <mergeCell ref="G15:G19"/>
+    <mergeCell ref="J15:J19"/>
+    <mergeCell ref="F20:F24"/>
+    <mergeCell ref="G20:G24"/>
+    <mergeCell ref="J20:J24"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="J30:J32"/>
+    <mergeCell ref="A35:A67"/>
+    <mergeCell ref="D35:D67"/>
+    <mergeCell ref="E35:E67"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="J35:J37"/>
+    <mergeCell ref="F38:F40"/>
+    <mergeCell ref="G38:G40"/>
+    <mergeCell ref="J38:J40"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="J41:J43"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="J44:J46"/>
+    <mergeCell ref="F47:F49"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="J47:J49"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="G50:G52"/>
+    <mergeCell ref="J50:J52"/>
+    <mergeCell ref="F53:F55"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="J53:J55"/>
+    <mergeCell ref="F56:F58"/>
+    <mergeCell ref="G56:G58"/>
+    <mergeCell ref="J56:J58"/>
+    <mergeCell ref="F59:F60"/>
+    <mergeCell ref="G59:G60"/>
+    <mergeCell ref="J59:J60"/>
+    <mergeCell ref="F61:F63"/>
+    <mergeCell ref="G61:G63"/>
+    <mergeCell ref="J61:J63"/>
+    <mergeCell ref="F64:F66"/>
+    <mergeCell ref="G64:G66"/>
+    <mergeCell ref="J64:J66"/>
+    <mergeCell ref="A68:A74"/>
+    <mergeCell ref="D68:D74"/>
+    <mergeCell ref="E68:E74"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="F70:F72"/>
+    <mergeCell ref="G70:G72"/>
+    <mergeCell ref="J70:J72"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="J73:J74"/>
+    <mergeCell ref="J119:J120"/>
+    <mergeCell ref="A75:A100"/>
+    <mergeCell ref="D75:D100"/>
+    <mergeCell ref="E75:E100"/>
+    <mergeCell ref="F75:F79"/>
+    <mergeCell ref="G75:G79"/>
+    <mergeCell ref="J75:J79"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="F85:F90"/>
+    <mergeCell ref="G85:G90"/>
+    <mergeCell ref="J85:J90"/>
+    <mergeCell ref="F91:F95"/>
+    <mergeCell ref="G91:G95"/>
+    <mergeCell ref="J91:J95"/>
+    <mergeCell ref="F96:F99"/>
+    <mergeCell ref="G96:G99"/>
+    <mergeCell ref="J96:J99"/>
     <mergeCell ref="A121:I121"/>
     <mergeCell ref="A102:A120"/>
     <mergeCell ref="D102:D120"/>
@@ -7047,100 +7165,6 @@
     <mergeCell ref="J116:J118"/>
     <mergeCell ref="F119:F120"/>
     <mergeCell ref="G119:G120"/>
-    <mergeCell ref="J119:J120"/>
-    <mergeCell ref="A75:A100"/>
-    <mergeCell ref="D75:D100"/>
-    <mergeCell ref="E75:E100"/>
-    <mergeCell ref="F75:F79"/>
-    <mergeCell ref="G75:G79"/>
-    <mergeCell ref="J75:J79"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="F85:F90"/>
-    <mergeCell ref="G85:G90"/>
-    <mergeCell ref="J85:J90"/>
-    <mergeCell ref="F91:F95"/>
-    <mergeCell ref="G91:G95"/>
-    <mergeCell ref="J91:J95"/>
-    <mergeCell ref="F96:F99"/>
-    <mergeCell ref="G96:G99"/>
-    <mergeCell ref="J96:J99"/>
-    <mergeCell ref="F61:F63"/>
-    <mergeCell ref="G61:G63"/>
-    <mergeCell ref="J61:J63"/>
-    <mergeCell ref="F64:F66"/>
-    <mergeCell ref="G64:G66"/>
-    <mergeCell ref="J64:J66"/>
-    <mergeCell ref="A68:A74"/>
-    <mergeCell ref="D68:D74"/>
-    <mergeCell ref="E68:E74"/>
-    <mergeCell ref="F68:F69"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="J68:J69"/>
-    <mergeCell ref="F70:F72"/>
-    <mergeCell ref="G70:G72"/>
-    <mergeCell ref="J70:J72"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="J73:J74"/>
-    <mergeCell ref="F53:F55"/>
-    <mergeCell ref="G53:G55"/>
-    <mergeCell ref="J53:J55"/>
-    <mergeCell ref="F56:F58"/>
-    <mergeCell ref="G56:G58"/>
-    <mergeCell ref="J56:J58"/>
-    <mergeCell ref="F59:F60"/>
-    <mergeCell ref="G59:G60"/>
-    <mergeCell ref="J59:J60"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="J30:J32"/>
-    <mergeCell ref="A35:A67"/>
-    <mergeCell ref="D35:D67"/>
-    <mergeCell ref="E35:E67"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="G35:G37"/>
-    <mergeCell ref="J35:J37"/>
-    <mergeCell ref="F38:F40"/>
-    <mergeCell ref="G38:G40"/>
-    <mergeCell ref="J38:J40"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="G41:G43"/>
-    <mergeCell ref="J41:J43"/>
-    <mergeCell ref="F44:F46"/>
-    <mergeCell ref="G44:G46"/>
-    <mergeCell ref="J44:J46"/>
-    <mergeCell ref="F47:F49"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="J47:J49"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="G50:G52"/>
-    <mergeCell ref="J50:J52"/>
-    <mergeCell ref="A2:A33"/>
-    <mergeCell ref="D2:D33"/>
-    <mergeCell ref="E2:E33"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="J2:J5"/>
-    <mergeCell ref="F6:F10"/>
-    <mergeCell ref="G6:G10"/>
-    <mergeCell ref="J6:J10"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="G11:G14"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="F15:F19"/>
-    <mergeCell ref="G15:G19"/>
-    <mergeCell ref="J15:J19"/>
-    <mergeCell ref="F20:F24"/>
-    <mergeCell ref="G20:G24"/>
-    <mergeCell ref="J20:J24"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="J25:J27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="J28:J29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7173,13 +7197,13 @@
       <c r="C1" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -7188,7 +7212,7 @@
       <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="17" t="s">
         <v>173</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -7196,25 +7220,25 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32">
+      <c r="B2" s="33">
         <v>46253</v>
       </c>
       <c r="C2" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="24" t="s">
         <v>147</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -7223,36 +7247,36 @@
       <c r="I2" s="8">
         <v>14</v>
       </c>
-      <c r="J2" s="17">
+      <c r="J2" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A3" s="15"/>
+      <c r="A3" s="25"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I3" s="8">
         <v>37</v>
       </c>
-      <c r="J3" s="19"/>
+      <c r="J3" s="29"/>
     </row>
     <row r="4" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A4" s="15"/>
+      <c r="A4" s="25"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="14" t="s">
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="24" t="s">
         <v>148</v>
       </c>
       <c r="H4" s="4" t="s">
@@ -7261,52 +7285,52 @@
       <c r="I4" s="8">
         <v>3</v>
       </c>
-      <c r="J4" s="17">
+      <c r="J4" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A5" s="15"/>
+      <c r="A5" s="25"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="4" t="s">
         <v>37</v>
       </c>
       <c r="I5" s="8">
         <v>36</v>
       </c>
-      <c r="J5" s="18"/>
+      <c r="J5" s="28"/>
     </row>
     <row r="6" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A6" s="15"/>
+      <c r="A6" s="25"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="8">
         <v>208</v>
       </c>
       <c r="I6" s="8">
         <v>12</v>
       </c>
-      <c r="J6" s="19"/>
+      <c r="J6" s="29"/>
     </row>
     <row r="7" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A7" s="15"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="14" t="s">
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="24" t="s">
         <v>150</v>
       </c>
       <c r="H7" s="8">
@@ -7315,52 +7339,52 @@
       <c r="I7" s="8">
         <v>15</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A8" s="15"/>
+      <c r="A8" s="25"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="8">
         <v>213</v>
       </c>
       <c r="I8" s="8">
         <v>24</v>
       </c>
-      <c r="J8" s="18"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A9" s="15"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
       <c r="H9" s="8">
         <v>216</v>
       </c>
       <c r="I9" s="8">
         <v>12</v>
       </c>
-      <c r="J9" s="19"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A10" s="15"/>
+      <c r="A10" s="25"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="14" t="s">
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="24" t="s">
         <v>151</v>
       </c>
       <c r="H10" s="8">
@@ -7369,52 +7393,52 @@
       <c r="I10" s="8">
         <v>12</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A11" s="15"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="8">
         <v>217</v>
       </c>
       <c r="I11" s="8">
         <v>24</v>
       </c>
-      <c r="J11" s="18"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="12" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A12" s="15"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="8">
         <v>218</v>
       </c>
       <c r="I12" s="8">
         <v>15</v>
       </c>
-      <c r="J12" s="19"/>
+      <c r="J12" s="29"/>
     </row>
     <row r="13" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A13" s="15"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="14" t="s">
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="24" t="s">
         <v>152</v>
       </c>
       <c r="H13" s="8">
@@ -7423,52 +7447,52 @@
       <c r="I13" s="8">
         <v>9</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A14" s="15"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
       <c r="H14" s="8">
         <v>219</v>
       </c>
       <c r="I14" s="8">
         <v>24</v>
       </c>
-      <c r="J14" s="18"/>
+      <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A15" s="15"/>
+      <c r="A15" s="25"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
       <c r="H15" s="8">
         <v>220</v>
       </c>
       <c r="I15" s="8">
         <v>18</v>
       </c>
-      <c r="J15" s="19"/>
+      <c r="J15" s="29"/>
     </row>
     <row r="16" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A16" s="15"/>
+      <c r="A16" s="25"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="14" t="s">
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="24" t="s">
         <v>153</v>
       </c>
       <c r="H16" s="8">
@@ -7477,52 +7501,52 @@
       <c r="I16" s="8">
         <v>6</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A17" s="15"/>
+      <c r="A17" s="25"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="8">
         <v>221</v>
       </c>
       <c r="I17" s="8">
         <v>24</v>
       </c>
-      <c r="J17" s="18"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A18" s="15"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
       <c r="H18" s="8">
         <v>222</v>
       </c>
       <c r="I18" s="8">
         <v>21</v>
       </c>
-      <c r="J18" s="19"/>
+      <c r="J18" s="29"/>
     </row>
     <row r="19" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A19" s="15"/>
+      <c r="A19" s="25"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="14" t="s">
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="24" t="s">
         <v>154</v>
       </c>
       <c r="H19" s="8">
@@ -7531,52 +7555,52 @@
       <c r="I19" s="8">
         <v>3</v>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A20" s="15"/>
+      <c r="A20" s="25"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
       <c r="H20" s="8">
         <v>223</v>
       </c>
       <c r="I20" s="8">
         <v>24</v>
       </c>
-      <c r="J20" s="18"/>
+      <c r="J20" s="28"/>
     </row>
     <row r="21" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A21" s="15"/>
+      <c r="A21" s="25"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
       <c r="H21" s="8">
         <v>224</v>
       </c>
       <c r="I21" s="8">
         <v>24</v>
       </c>
-      <c r="J21" s="19"/>
+      <c r="J21" s="29"/>
     </row>
     <row r="22" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A22" s="15"/>
+      <c r="A22" s="25"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="14" t="s">
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="24" t="s">
         <v>155</v>
       </c>
       <c r="H22" s="8">
@@ -7585,52 +7609,52 @@
       <c r="I22" s="8">
         <v>24</v>
       </c>
-      <c r="J22" s="17">
+      <c r="J22" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A23" s="15"/>
+      <c r="A23" s="25"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
       <c r="H23" s="8">
         <v>304</v>
       </c>
       <c r="I23" s="8">
         <v>24</v>
       </c>
-      <c r="J23" s="18"/>
+      <c r="J23" s="28"/>
     </row>
     <row r="24" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A24" s="15"/>
+      <c r="A24" s="25"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
       <c r="H24" s="8">
         <v>305</v>
       </c>
       <c r="I24" s="8">
         <v>3</v>
       </c>
-      <c r="J24" s="19"/>
+      <c r="J24" s="29"/>
     </row>
     <row r="25" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A25" s="15"/>
+      <c r="A25" s="25"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="14" t="s">
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="24" t="s">
         <v>156</v>
       </c>
       <c r="H25" s="8">
@@ -7639,52 +7663,52 @@
       <c r="I25" s="8">
         <v>21</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A26" s="15"/>
+      <c r="A26" s="25"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
       <c r="H26" s="8">
         <v>306</v>
       </c>
       <c r="I26" s="8">
         <v>24</v>
       </c>
-      <c r="J26" s="18"/>
+      <c r="J26" s="28"/>
     </row>
     <row r="27" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A27" s="15"/>
+      <c r="A27" s="25"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
       <c r="H27" s="8">
         <v>307</v>
       </c>
       <c r="I27" s="8">
         <v>6</v>
       </c>
-      <c r="J27" s="19"/>
+      <c r="J27" s="29"/>
     </row>
     <row r="28" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A28" s="15"/>
+      <c r="A28" s="25"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="14" t="s">
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="G28" s="24" t="s">
         <v>158</v>
       </c>
       <c r="H28" s="8">
@@ -7693,52 +7717,52 @@
       <c r="I28" s="8">
         <v>22</v>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A29" s="15"/>
+      <c r="A29" s="25"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
       <c r="H29" s="4" t="s">
         <v>53</v>
       </c>
       <c r="I29" s="8">
         <v>24</v>
       </c>
-      <c r="J29" s="18"/>
+      <c r="J29" s="28"/>
     </row>
     <row r="30" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A30" s="15"/>
+      <c r="A30" s="25"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="4" t="s">
         <v>55</v>
       </c>
       <c r="I30" s="8">
         <v>5</v>
       </c>
-      <c r="J30" s="19"/>
+      <c r="J30" s="29"/>
     </row>
     <row r="31" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A31" s="15"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="14" t="s">
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="24" t="s">
         <v>159</v>
       </c>
       <c r="H31" s="4" t="s">
@@ -7747,32 +7771,32 @@
       <c r="I31" s="8">
         <v>19</v>
       </c>
-      <c r="J31" s="17">
+      <c r="J31" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A32" s="15"/>
+      <c r="A32" s="25"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="8">
         <v>320</v>
       </c>
       <c r="I32" s="8">
         <v>32</v>
       </c>
-      <c r="J32" s="19"/>
+      <c r="J32" s="29"/>
     </row>
     <row r="33" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A33" s="16"/>
+      <c r="A33" s="26"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
       <c r="F33" s="4" t="s">
         <v>157</v>
       </c>
@@ -7791,47 +7815,47 @@
     </row>
     <row r="34" spans="1:10" ht="0.95" customHeight="1"/>
     <row r="35" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A35" s="20"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
       <c r="H35" s="4" t="s">
         <v>110</v>
       </c>
       <c r="I35" s="8">
         <v>25</v>
       </c>
-      <c r="J35" s="26"/>
+      <c r="J35" s="30"/>
     </row>
     <row r="36" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A36" s="21"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
       <c r="H36" s="4" t="s">
         <v>113</v>
       </c>
       <c r="I36" s="8">
         <v>11</v>
       </c>
-      <c r="J36" s="27"/>
+      <c r="J36" s="31"/>
     </row>
     <row r="37" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A37" s="21"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="14" t="s">
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G37" s="14" t="s">
+      <c r="G37" s="24" t="s">
         <v>161</v>
       </c>
       <c r="H37" s="4" t="s">
@@ -7840,52 +7864,52 @@
       <c r="I37" s="8">
         <v>14</v>
       </c>
-      <c r="J37" s="17">
+      <c r="J37" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A38" s="21"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
       <c r="H38" s="4" t="s">
         <v>114</v>
       </c>
       <c r="I38" s="8">
         <v>25</v>
       </c>
-      <c r="J38" s="18"/>
+      <c r="J38" s="28"/>
     </row>
     <row r="39" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A39" s="21"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
       <c r="H39" s="4" t="s">
         <v>117</v>
       </c>
       <c r="I39" s="8">
         <v>12</v>
       </c>
-      <c r="J39" s="19"/>
+      <c r="J39" s="29"/>
     </row>
     <row r="40" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A40" s="21"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="14" t="s">
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="G40" s="14" t="s">
+      <c r="G40" s="24" t="s">
         <v>162</v>
       </c>
       <c r="H40" s="4" t="s">
@@ -7894,52 +7918,52 @@
       <c r="I40" s="8">
         <v>13</v>
       </c>
-      <c r="J40" s="17">
+      <c r="J40" s="27">
         <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A41" s="21"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
       <c r="H41" s="4" t="s">
         <v>118</v>
       </c>
       <c r="I41" s="8">
         <v>25</v>
       </c>
-      <c r="J41" s="18"/>
+      <c r="J41" s="28"/>
     </row>
     <row r="42" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A42" s="21"/>
+      <c r="A42" s="22"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
       <c r="H42" s="4" t="s">
         <v>120</v>
       </c>
       <c r="I42" s="8">
         <v>13</v>
       </c>
-      <c r="J42" s="19"/>
+      <c r="J42" s="29"/>
     </row>
     <row r="43" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A43" s="21"/>
+      <c r="A43" s="22"/>
       <c r="B43" s="10"/>
       <c r="C43" s="10"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="14" t="s">
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="G43" s="14" t="s">
+      <c r="G43" s="24" t="s">
         <v>164</v>
       </c>
       <c r="H43" s="4" t="s">
@@ -7948,52 +7972,52 @@
       <c r="I43" s="8">
         <v>12</v>
       </c>
-      <c r="J43" s="17">
+      <c r="J43" s="27">
         <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A44" s="21"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="10"/>
       <c r="C44" s="10"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
       <c r="H44" s="8">
         <v>514</v>
       </c>
       <c r="I44" s="8">
         <v>24</v>
       </c>
-      <c r="J44" s="18"/>
+      <c r="J44" s="28"/>
     </row>
     <row r="45" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A45" s="21"/>
+      <c r="A45" s="22"/>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
       <c r="H45" s="8">
         <v>515</v>
       </c>
       <c r="I45" s="8">
         <v>16</v>
       </c>
-      <c r="J45" s="19"/>
+      <c r="J45" s="29"/>
     </row>
     <row r="46" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A46" s="21"/>
+      <c r="A46" s="22"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="14" t="s">
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="G46" s="14" t="s">
+      <c r="G46" s="24" t="s">
         <v>166</v>
       </c>
       <c r="H46" s="8">
@@ -8002,67 +8026,92 @@
       <c r="I46" s="8">
         <v>8</v>
       </c>
-      <c r="J46" s="17">
+      <c r="J46" s="27">
         <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A47" s="21"/>
+      <c r="A47" s="22"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
       <c r="H47" s="8">
         <v>516</v>
       </c>
       <c r="I47" s="8">
         <v>24</v>
       </c>
-      <c r="J47" s="18"/>
+      <c r="J47" s="28"/>
     </row>
     <row r="48" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A48" s="22"/>
+      <c r="A48" s="23"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
       <c r="H48" s="4" t="s">
         <v>123</v>
       </c>
       <c r="I48" s="8">
         <v>20</v>
       </c>
-      <c r="J48" s="19"/>
+      <c r="J48" s="29"/>
     </row>
     <row r="49" spans="1:10" ht="19.7" customHeight="1">
-      <c r="A49" s="23" t="s">
+      <c r="A49" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B49" s="24"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="25"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="20"/>
       <c r="J49" s="8">
         <v>818</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="F43:F45"/>
-    <mergeCell ref="G43:G45"/>
-    <mergeCell ref="J43:J45"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="G46:G48"/>
-    <mergeCell ref="J46:J48"/>
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="D2:D33"/>
+    <mergeCell ref="E2:E33"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="J7:J9"/>
+    <mergeCell ref="J10:J12"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="J25:J27"/>
     <mergeCell ref="J28:J30"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
@@ -8079,38 +8128,13 @@
     <mergeCell ref="F40:F42"/>
     <mergeCell ref="G40:G42"/>
     <mergeCell ref="J40:J42"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="J25:J27"/>
-    <mergeCell ref="J10:J12"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="J13:J15"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="J4:J6"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="J7:J9"/>
-    <mergeCell ref="A2:A33"/>
-    <mergeCell ref="D2:D33"/>
-    <mergeCell ref="E2:E33"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="J43:J45"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="J46:J48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
